--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/06,26/25,06,26 Останкино СЫР/Дв.Останкино Сыр от 22,06,26, Донецк.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/06,26/25,06,26 Останкино СЫР/Дв.Останкино Сыр от 22,06,26, Донецк.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\Заказы на отправку и сортировку\Останкино\Останкино исходники\СЫРЫ\Донецк\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\06,26\25,06,26 Останкино СЫР\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE39DD30-373F-4AA9-BD2B-7929FFDCB220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B43E78A-2560-4460-B917-1DBB08D877D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="81">
   <si>
     <t>Ведомость по товарам на складах</t>
   </si>
@@ -272,7 +272,7 @@
     <t>ср.днев.</t>
   </si>
   <si>
-    <t>ЗАКАЗ</t>
+    <t>заказ</t>
   </si>
 </sst>
 </file>
@@ -282,7 +282,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0_ ;[Red]\-0\ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <name val="Arial"/>
@@ -319,6 +319,32 @@
       <b/>
       <sz val="8"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
@@ -421,7 +447,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -480,9 +506,31 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{63B11A9E-AF2E-40F9-8D8F-7CA7C2D971A2}"/>
@@ -8644,18 +8692,34 @@
     <col min="10" max="10" width="4.33203125" customWidth="1"/>
     <col min="11" max="12" width="8.5" customWidth="1"/>
     <col min="13" max="14" width="1.5" customWidth="1"/>
-    <col min="15" max="24" width="8.5" customWidth="1"/>
+    <col min="15" max="16" width="8.5" customWidth="1"/>
+    <col min="17" max="17" width="8.5" style="30" customWidth="1"/>
+    <col min="18" max="18" width="8.5" style="25" customWidth="1"/>
+    <col min="19" max="21" width="8.5" style="30" customWidth="1"/>
+    <col min="22" max="24" width="8.5" customWidth="1"/>
     <col min="25" max="28" width="7" customWidth="1"/>
     <col min="29" max="32" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1" spans="1:64" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q1" s="29"/>
+      <c r="R1" s="24"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+    </row>
     <row r="2" spans="1:64" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:64" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:64" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q3" s="29"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="29"/>
+      <c r="T3" s="29"/>
+      <c r="U3" s="29"/>
+    </row>
     <row r="4" spans="1:64" ht="12.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>1</v>
@@ -8676,21 +8740,17 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
-      <c r="S6" t="s">
-        <v>77</v>
-      </c>
-      <c r="U6" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="7" spans="1:64" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="R7" s="24" t="s">
+      <c r="Q7" s="29"/>
+      <c r="R7" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="S7" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="S7" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="U7" s="24" t="s">
+      <c r="T7" s="29"/>
+      <c r="U7" s="31" t="s">
         <v>76</v>
       </c>
     </row>
@@ -8743,19 +8803,19 @@
       <c r="P8" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="Q8" s="14" t="s">
+      <c r="Q8" s="32" t="s">
         <v>60</v>
       </c>
       <c r="R8" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="S8" s="15" t="s">
+      <c r="S8" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="T8" s="15" t="s">
+      <c r="T8" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="U8" s="15" t="s">
+      <c r="U8" s="33" t="s">
         <v>61</v>
       </c>
       <c r="V8" s="15" t="s">
@@ -8816,7 +8876,9 @@
       <c r="Q9" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="R9" s="16"/>
+      <c r="R9" s="26" t="s">
+        <v>70</v>
+      </c>
       <c r="S9" s="16" t="s">
         <v>70</v>
       </c>
@@ -8894,20 +8956,20 @@
         <f t="shared" si="1"/>
         <v>611.33759999999984</v>
       </c>
-      <c r="Q10" s="19">
+      <c r="Q10" s="34">
         <f t="shared" si="1"/>
         <v>5200.768</v>
       </c>
-      <c r="R10" s="19">
+      <c r="R10" s="27">
         <f t="shared" si="1"/>
         <v>5248</v>
       </c>
-      <c r="S10" s="19">
+      <c r="S10" s="34">
         <f t="shared" si="1"/>
         <v>2265</v>
       </c>
       <c r="T10" s="16"/>
-      <c r="U10" s="19">
+      <c r="U10" s="34">
         <f>SUM(U11:U351)</f>
         <v>2983</v>
       </c>
@@ -8994,17 +9056,17 @@
         <f>E11/5</f>
         <v>10.0276</v>
       </c>
-      <c r="Q11" s="20"/>
+      <c r="Q11" s="35"/>
       <c r="R11" s="20">
         <f>S11</f>
         <v>0</v>
       </c>
-      <c r="S11" s="20">
+      <c r="S11" s="35">
         <f>VLOOKUP(A11,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T11" s="9"/>
-      <c r="U11" s="20">
+      <c r="T11" s="36"/>
+      <c r="U11" s="35">
         <f>VLOOKUP(A11,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -9130,17 +9192,17 @@
         <f t="shared" ref="P12:P49" si="3">E12/5</f>
         <v>0.4</v>
       </c>
-      <c r="Q12" s="20"/>
+      <c r="Q12" s="35"/>
       <c r="R12" s="20">
         <f t="shared" ref="R12:R49" si="4">S12</f>
         <v>0</v>
       </c>
-      <c r="S12" s="20">
+      <c r="S12" s="35">
         <f>VLOOKUP(A12,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T12" s="9"/>
-      <c r="U12" s="20">
+      <c r="T12" s="36"/>
+      <c r="U12" s="35">
         <f>VLOOKUP(A12,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -9266,17 +9328,17 @@
         <f t="shared" si="3"/>
         <v>0.4</v>
       </c>
-      <c r="Q13" s="20"/>
+      <c r="Q13" s="35"/>
       <c r="R13" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S13" s="20">
+      <c r="S13" s="35">
         <f>VLOOKUP(A13,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T13" s="9"/>
-      <c r="U13" s="20">
+      <c r="T13" s="36"/>
+      <c r="U13" s="35">
         <f>VLOOKUP(A13,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -9401,17 +9463,17 @@
         <f t="shared" si="3"/>
         <v>3.3479999999999999</v>
       </c>
-      <c r="Q14" s="20"/>
+      <c r="Q14" s="35"/>
       <c r="R14" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S14" s="20">
+      <c r="S14" s="35">
         <f>VLOOKUP(A14,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T14" s="9"/>
-      <c r="U14" s="20">
+      <c r="T14" s="36"/>
+      <c r="U14" s="35">
         <f>VLOOKUP(A14,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -9537,17 +9599,17 @@
         <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
-      <c r="Q15" s="20"/>
+      <c r="Q15" s="35"/>
       <c r="R15" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S15" s="20">
+      <c r="S15" s="35">
         <f>VLOOKUP(A15,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T15" s="9"/>
-      <c r="U15" s="20">
+      <c r="T15" s="36"/>
+      <c r="U15" s="35">
         <f>VLOOKUP(A15,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -9673,17 +9735,17 @@
         <f t="shared" si="3"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="Q16" s="20"/>
+      <c r="Q16" s="35"/>
       <c r="R16" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S16" s="20">
+      <c r="S16" s="35">
         <f>VLOOKUP(A16,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T16" s="9"/>
-      <c r="U16" s="20">
+      <c r="T16" s="36"/>
+      <c r="U16" s="35">
         <f>VLOOKUP(A16,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -9809,17 +9871,17 @@
         <f t="shared" si="3"/>
         <v>3.2</v>
       </c>
-      <c r="Q17" s="20"/>
+      <c r="Q17" s="35"/>
       <c r="R17" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S17" s="20">
+      <c r="S17" s="35">
         <f>VLOOKUP(A17,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T17" s="9"/>
-      <c r="U17" s="20">
+      <c r="T17" s="36"/>
+      <c r="U17" s="35">
         <f>VLOOKUP(A17,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -9945,17 +10007,17 @@
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="Q18" s="20"/>
+      <c r="Q18" s="35"/>
       <c r="R18" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S18" s="20">
+      <c r="S18" s="35">
         <f>VLOOKUP(A18,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T18" s="9"/>
-      <c r="U18" s="20">
+      <c r="T18" s="36"/>
+      <c r="U18" s="35">
         <f>VLOOKUP(A18,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -10081,17 +10143,17 @@
         <f t="shared" si="3"/>
         <v>7.2</v>
       </c>
-      <c r="Q19" s="20"/>
+      <c r="Q19" s="35"/>
       <c r="R19" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S19" s="20">
+      <c r="S19" s="35">
         <f>VLOOKUP(A19,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T19" s="9"/>
-      <c r="U19" s="20">
+      <c r="T19" s="36"/>
+      <c r="U19" s="35">
         <f>VLOOKUP(A19,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -10219,17 +10281,17 @@
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="Q20" s="20"/>
+      <c r="Q20" s="35"/>
       <c r="R20" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S20" s="20">
+      <c r="S20" s="35">
         <f>VLOOKUP(A20,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T20" s="9"/>
-      <c r="U20" s="20">
+      <c r="T20" s="36"/>
+      <c r="U20" s="35">
         <f>VLOOKUP(A20,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -10357,7 +10419,7 @@
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="Q21" s="20">
+      <c r="Q21" s="35">
         <f>P21*20-F21-O21</f>
         <v>50</v>
       </c>
@@ -10365,12 +10427,12 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S21" s="20">
+      <c r="S21" s="35">
         <f>VLOOKUP(A21,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T21" s="9"/>
-      <c r="U21" s="20">
+      <c r="T21" s="36"/>
+      <c r="U21" s="35">
         <f>VLOOKUP(A21,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -10498,20 +10560,20 @@
         <f t="shared" si="3"/>
         <v>59</v>
       </c>
-      <c r="Q22" s="20">
-        <f t="shared" ref="Q21:Q49" si="10">P22*20-F22-O22</f>
+      <c r="Q22" s="35">
+        <f t="shared" ref="Q22:Q49" si="10">P22*20-F22-O22</f>
         <v>442</v>
       </c>
       <c r="R22" s="20">
         <f>S22+U22</f>
         <v>442</v>
       </c>
-      <c r="S22" s="20">
+      <c r="S22" s="35">
         <f>VLOOKUP(A22,[3]TDSheet!$A:$R,18,0)</f>
         <v>200</v>
       </c>
-      <c r="T22" s="9"/>
-      <c r="U22" s="20">
+      <c r="T22" s="36"/>
+      <c r="U22" s="35">
         <f>VLOOKUP(A22,[4]TDSheet!$A:$R,18,0)</f>
         <v>242</v>
       </c>
@@ -10637,7 +10699,7 @@
         <f t="shared" si="3"/>
         <v>28.6</v>
       </c>
-      <c r="Q23" s="20">
+      <c r="Q23" s="35">
         <f t="shared" si="10"/>
         <v>135</v>
       </c>
@@ -10645,12 +10707,12 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S23" s="20">
+      <c r="S23" s="35">
         <f>VLOOKUP(A23,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T23" s="9"/>
-      <c r="U23" s="20">
+      <c r="T23" s="36"/>
+      <c r="U23" s="35">
         <f>VLOOKUP(A23,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -10776,17 +10838,17 @@
         <f t="shared" si="3"/>
         <v>1.6</v>
       </c>
-      <c r="Q24" s="20"/>
+      <c r="Q24" s="35"/>
       <c r="R24" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S24" s="20">
+      <c r="S24" s="35">
         <f>VLOOKUP(A24,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T24" s="9"/>
-      <c r="U24" s="20">
+      <c r="T24" s="36"/>
+      <c r="U24" s="35">
         <f>VLOOKUP(A24,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -10912,17 +10974,17 @@
         <f t="shared" si="3"/>
         <v>0.2</v>
       </c>
-      <c r="Q25" s="20"/>
+      <c r="Q25" s="35"/>
       <c r="R25" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S25" s="20">
+      <c r="S25" s="35">
         <f>VLOOKUP(A25,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T25" s="9"/>
-      <c r="U25" s="20">
+      <c r="T25" s="36"/>
+      <c r="U25" s="35">
         <f>VLOOKUP(A25,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -11050,17 +11112,17 @@
         <f t="shared" si="3"/>
         <v>5.4</v>
       </c>
-      <c r="Q26" s="20"/>
+      <c r="Q26" s="35"/>
       <c r="R26" s="20">
         <f t="shared" ref="R26:R31" si="11">S26+U26</f>
         <v>100</v>
       </c>
-      <c r="S26" s="20">
+      <c r="S26" s="35">
         <f>VLOOKUP(A26,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T26" s="9"/>
-      <c r="U26" s="20">
+      <c r="T26" s="36"/>
+      <c r="U26" s="35">
         <f>VLOOKUP(A26,[4]TDSheet!$A:$R,18,0)</f>
         <v>100</v>
       </c>
@@ -11188,17 +11250,17 @@
         <f t="shared" si="3"/>
         <v>19.600000000000001</v>
       </c>
-      <c r="Q27" s="20"/>
+      <c r="Q27" s="35"/>
       <c r="R27" s="20">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="S27" s="20">
+      <c r="S27" s="35">
         <f>VLOOKUP(A27,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T27" s="9"/>
-      <c r="U27" s="20">
+      <c r="T27" s="36"/>
+      <c r="U27" s="35">
         <f>VLOOKUP(A27,[4]TDSheet!$A:$R,18,0)</f>
         <v>100</v>
       </c>
@@ -11324,7 +11386,7 @@
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="Q28" s="20">
+      <c r="Q28" s="35">
         <f t="shared" si="10"/>
         <v>327</v>
       </c>
@@ -11332,12 +11394,12 @@
         <f t="shared" si="11"/>
         <v>327</v>
       </c>
-      <c r="S28" s="20">
+      <c r="S28" s="35">
         <f>VLOOKUP(A28,[3]TDSheet!$A:$R,18,0)</f>
         <v>200</v>
       </c>
-      <c r="T28" s="9"/>
-      <c r="U28" s="20">
+      <c r="T28" s="36"/>
+      <c r="U28" s="35">
         <f>VLOOKUP(A28,[4]TDSheet!$A:$R,18,0)</f>
         <v>127</v>
       </c>
@@ -11465,7 +11527,7 @@
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="Q29" s="20">
+      <c r="Q29" s="35">
         <f t="shared" si="10"/>
         <v>258</v>
       </c>
@@ -11473,12 +11535,12 @@
         <f t="shared" si="11"/>
         <v>258</v>
       </c>
-      <c r="S29" s="20">
+      <c r="S29" s="35">
         <f>VLOOKUP(A29,[3]TDSheet!$A:$R,18,0)</f>
         <v>200</v>
       </c>
-      <c r="T29" s="9"/>
-      <c r="U29" s="20">
+      <c r="T29" s="36"/>
+      <c r="U29" s="35">
         <f>VLOOKUP(A29,[4]TDSheet!$A:$R,18,0)</f>
         <v>58</v>
       </c>
@@ -11606,7 +11668,7 @@
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="Q30" s="20">
+      <c r="Q30" s="35">
         <f t="shared" si="10"/>
         <v>154</v>
       </c>
@@ -11614,12 +11676,12 @@
         <f t="shared" si="11"/>
         <v>154</v>
       </c>
-      <c r="S30" s="20">
+      <c r="S30" s="35">
         <f>VLOOKUP(A30,[3]TDSheet!$A:$R,18,0)</f>
         <v>54</v>
       </c>
-      <c r="T30" s="9"/>
-      <c r="U30" s="20">
+      <c r="T30" s="36"/>
+      <c r="U30" s="35">
         <f>VLOOKUP(A30,[4]TDSheet!$A:$R,18,0)</f>
         <v>100</v>
       </c>
@@ -11747,7 +11809,7 @@
         <f t="shared" si="3"/>
         <v>64.599999999999994</v>
       </c>
-      <c r="Q31" s="20">
+      <c r="Q31" s="35">
         <f t="shared" si="10"/>
         <v>995</v>
       </c>
@@ -11755,12 +11817,12 @@
         <f t="shared" si="11"/>
         <v>995</v>
       </c>
-      <c r="S31" s="20">
+      <c r="S31" s="35">
         <f>VLOOKUP(A31,[3]TDSheet!$A:$R,18,0)</f>
         <v>495</v>
       </c>
-      <c r="T31" s="9"/>
-      <c r="U31" s="20">
+      <c r="T31" s="36"/>
+      <c r="U31" s="35">
         <f>VLOOKUP(A31,[4]TDSheet!$A:$R,18,0)</f>
         <v>500</v>
       </c>
@@ -11888,17 +11950,17 @@
         <f t="shared" si="3"/>
         <v>3.4</v>
       </c>
-      <c r="Q32" s="20"/>
+      <c r="Q32" s="35"/>
       <c r="R32" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S32" s="20">
+      <c r="S32" s="35">
         <f>VLOOKUP(A32,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T32" s="9"/>
-      <c r="U32" s="20">
+      <c r="T32" s="36"/>
+      <c r="U32" s="35">
         <f>VLOOKUP(A32,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -12026,17 +12088,17 @@
         <f t="shared" si="3"/>
         <v>1.4</v>
       </c>
-      <c r="Q33" s="20"/>
+      <c r="Q33" s="35"/>
       <c r="R33" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S33" s="20">
+      <c r="S33" s="35">
         <f>VLOOKUP(A33,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T33" s="9"/>
-      <c r="U33" s="20">
+      <c r="T33" s="36"/>
+      <c r="U33" s="35">
         <f>VLOOKUP(A33,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -12164,7 +12226,7 @@
         <f t="shared" si="3"/>
         <v>126.4</v>
       </c>
-      <c r="Q34" s="20">
+      <c r="Q34" s="35">
         <f t="shared" si="10"/>
         <v>1814</v>
       </c>
@@ -12172,12 +12234,12 @@
         <f t="shared" ref="R34:R35" si="12">S34+U34</f>
         <v>1600</v>
       </c>
-      <c r="S34" s="20">
+      <c r="S34" s="35">
         <f>VLOOKUP(A34,[3]TDSheet!$A:$R,18,0)</f>
         <v>600</v>
       </c>
-      <c r="T34" s="9"/>
-      <c r="U34" s="20">
+      <c r="T34" s="36"/>
+      <c r="U34" s="35">
         <f>VLOOKUP(A34,[4]TDSheet!$A:$R,18,0)</f>
         <v>1000</v>
       </c>
@@ -12305,17 +12367,17 @@
         <f t="shared" si="3"/>
         <v>26.2</v>
       </c>
-      <c r="Q35" s="20"/>
+      <c r="Q35" s="35"/>
       <c r="R35" s="20">
         <f t="shared" si="12"/>
         <v>150</v>
       </c>
-      <c r="S35" s="20">
+      <c r="S35" s="35">
         <f>VLOOKUP(A35,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T35" s="9"/>
-      <c r="U35" s="20">
+      <c r="T35" s="36"/>
+      <c r="U35" s="35">
         <f>VLOOKUP(A35,[4]TDSheet!$A:$R,18,0)</f>
         <v>150</v>
       </c>
@@ -12443,17 +12505,17 @@
         <f t="shared" si="3"/>
         <v>9.4</v>
       </c>
-      <c r="Q36" s="20"/>
+      <c r="Q36" s="35"/>
       <c r="R36" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S36" s="20">
+      <c r="S36" s="35">
         <f>VLOOKUP(A36,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T36" s="9"/>
-      <c r="U36" s="20">
+      <c r="T36" s="36"/>
+      <c r="U36" s="35">
         <f>VLOOKUP(A36,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -12581,17 +12643,17 @@
         <f t="shared" si="3"/>
         <v>2.7472000000000003</v>
       </c>
-      <c r="Q37" s="20"/>
+      <c r="Q37" s="35"/>
       <c r="R37" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S37" s="20">
+      <c r="S37" s="35">
         <f>VLOOKUP(A37,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T37" s="9"/>
-      <c r="U37" s="20">
+      <c r="T37" s="36"/>
+      <c r="U37" s="35">
         <f>VLOOKUP(A37,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -12719,17 +12781,17 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q38" s="20"/>
+      <c r="Q38" s="35"/>
       <c r="R38" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S38" s="20">
+      <c r="S38" s="35">
         <f>VLOOKUP(A38,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T38" s="9"/>
-      <c r="U38" s="20">
+      <c r="T38" s="36"/>
+      <c r="U38" s="35">
         <f>VLOOKUP(A38,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -12857,17 +12919,17 @@
         <f t="shared" si="3"/>
         <v>6.0739999999999998</v>
       </c>
-      <c r="Q39" s="20"/>
+      <c r="Q39" s="35"/>
       <c r="R39" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S39" s="20">
+      <c r="S39" s="35">
         <f>VLOOKUP(A39,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T39" s="9"/>
-      <c r="U39" s="20">
+      <c r="T39" s="36"/>
+      <c r="U39" s="35">
         <f>VLOOKUP(A39,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -12995,17 +13057,17 @@
         <f t="shared" si="3"/>
         <v>0.64160000000000006</v>
       </c>
-      <c r="Q40" s="20"/>
+      <c r="Q40" s="35"/>
       <c r="R40" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S40" s="20">
+      <c r="S40" s="35">
         <f>VLOOKUP(A40,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T40" s="9"/>
-      <c r="U40" s="20">
+      <c r="T40" s="36"/>
+      <c r="U40" s="35">
         <f>VLOOKUP(A40,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -13133,7 +13195,7 @@
         <f t="shared" si="3"/>
         <v>48.2</v>
       </c>
-      <c r="Q41" s="20">
+      <c r="Q41" s="35">
         <f t="shared" si="10"/>
         <v>515</v>
       </c>
@@ -13141,12 +13203,12 @@
         <f t="shared" ref="R41:R42" si="13">S41+U41</f>
         <v>515</v>
       </c>
-      <c r="S41" s="20">
+      <c r="S41" s="35">
         <f>VLOOKUP(A41,[3]TDSheet!$A:$R,18,0)</f>
         <v>200</v>
       </c>
-      <c r="T41" s="9"/>
-      <c r="U41" s="20">
+      <c r="T41" s="36"/>
+      <c r="U41" s="35">
         <f>VLOOKUP(A41,[4]TDSheet!$A:$R,18,0)</f>
         <v>315</v>
       </c>
@@ -13274,7 +13336,7 @@
         <f t="shared" si="3"/>
         <v>44.8</v>
       </c>
-      <c r="Q42" s="20">
+      <c r="Q42" s="35">
         <f t="shared" si="10"/>
         <v>231</v>
       </c>
@@ -13282,12 +13344,12 @@
         <f t="shared" si="13"/>
         <v>231</v>
       </c>
-      <c r="S42" s="20">
+      <c r="S42" s="35">
         <f>VLOOKUP(A42,[3]TDSheet!$A:$R,18,0)</f>
         <v>81</v>
       </c>
-      <c r="T42" s="9"/>
-      <c r="U42" s="20">
+      <c r="T42" s="36"/>
+      <c r="U42" s="35">
         <f>VLOOKUP(A42,[4]TDSheet!$A:$R,18,0)</f>
         <v>150</v>
       </c>
@@ -13413,17 +13475,17 @@
         <f t="shared" si="3"/>
         <v>0.9012</v>
       </c>
-      <c r="Q43" s="20"/>
+      <c r="Q43" s="35"/>
       <c r="R43" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S43" s="20">
+      <c r="S43" s="35">
         <f>VLOOKUP(A43,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T43" s="9"/>
-      <c r="U43" s="20">
+      <c r="T43" s="36"/>
+      <c r="U43" s="35">
         <f>VLOOKUP(A43,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -13551,7 +13613,7 @@
         <f t="shared" si="3"/>
         <v>8.8000000000000007</v>
       </c>
-      <c r="Q44" s="20">
+      <c r="Q44" s="35">
         <f t="shared" si="10"/>
         <v>60</v>
       </c>
@@ -13559,12 +13621,12 @@
         <f t="shared" ref="R44:R45" si="14">S44+U44</f>
         <v>60</v>
       </c>
-      <c r="S44" s="20">
+      <c r="S44" s="35">
         <f>VLOOKUP(A44,[3]TDSheet!$A:$R,18,0)</f>
         <v>30</v>
       </c>
-      <c r="T44" s="9"/>
-      <c r="U44" s="20">
+      <c r="T44" s="36"/>
+      <c r="U44" s="35">
         <f>VLOOKUP(A44,[4]TDSheet!$A:$R,18,0)</f>
         <v>30</v>
       </c>
@@ -13692,7 +13754,7 @@
         <f t="shared" si="3"/>
         <v>11.6</v>
       </c>
-      <c r="Q45" s="20">
+      <c r="Q45" s="35">
         <f t="shared" si="10"/>
         <v>115</v>
       </c>
@@ -13700,12 +13762,12 @@
         <f t="shared" si="14"/>
         <v>125</v>
       </c>
-      <c r="S45" s="20">
+      <c r="S45" s="35">
         <f>VLOOKUP(A45,[3]TDSheet!$A:$R,18,0)</f>
         <v>55</v>
       </c>
-      <c r="T45" s="9"/>
-      <c r="U45" s="20">
+      <c r="T45" s="36"/>
+      <c r="U45" s="35">
         <f>VLOOKUP(A45,[4]TDSheet!$A:$R,18,0)</f>
         <v>70</v>
       </c>
@@ -13833,17 +13895,17 @@
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="Q46" s="20"/>
+      <c r="Q46" s="35"/>
       <c r="R46" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S46" s="20">
+      <c r="S46" s="35">
         <f>VLOOKUP(A46,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T46" s="9"/>
-      <c r="U46" s="20">
+      <c r="T46" s="36"/>
+      <c r="U46" s="35">
         <f>VLOOKUP(A46,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -13969,17 +14031,17 @@
         <f t="shared" si="3"/>
         <v>0.70960000000000001</v>
       </c>
-      <c r="Q47" s="20"/>
+      <c r="Q47" s="35"/>
       <c r="R47" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S47" s="20">
+      <c r="S47" s="35">
         <f>VLOOKUP(A47,[3]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
-      <c r="T47" s="9"/>
-      <c r="U47" s="20">
+      <c r="T47" s="36"/>
+      <c r="U47" s="35">
         <f>VLOOKUP(A47,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -14107,7 +14169,7 @@
         <f t="shared" si="3"/>
         <v>12.8</v>
       </c>
-      <c r="Q48" s="20">
+      <c r="Q48" s="35">
         <f t="shared" si="10"/>
         <v>91</v>
       </c>
@@ -14115,12 +14177,12 @@
         <f>S48+U48</f>
         <v>91</v>
       </c>
-      <c r="S48" s="20">
+      <c r="S48" s="35">
         <f>VLOOKUP(A48,[3]TDSheet!$A:$R,18,0)</f>
         <v>50</v>
       </c>
-      <c r="T48" s="9"/>
-      <c r="U48" s="20">
+      <c r="T48" s="36"/>
+      <c r="U48" s="35">
         <f>VLOOKUP(A48,[4]TDSheet!$A:$R,18,0)</f>
         <v>41</v>
       </c>
@@ -14244,7 +14306,7 @@
         <f t="shared" si="3"/>
         <v>0.68840000000000001</v>
       </c>
-      <c r="Q49" s="20">
+      <c r="Q49" s="35">
         <f t="shared" si="10"/>
         <v>13.768000000000001</v>
       </c>
@@ -14252,12 +14314,12 @@
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="S49" s="20">
+      <c r="S49" s="35">
         <f>VLOOKUP(A49,[3]TDSheet!$A:$R,18,0)</f>
         <v>100</v>
       </c>
-      <c r="T49" s="9"/>
-      <c r="U49" s="20">
+      <c r="T49" s="36"/>
+      <c r="U49" s="35">
         <f>VLOOKUP(A49,[4]TDSheet!$A:$R,18,0)</f>
         <v>0</v>
       </c>
@@ -14350,11 +14412,11 @@
       <c r="N50" s="9"/>
       <c r="O50" s="9"/>
       <c r="P50" s="9"/>
-      <c r="Q50" s="9"/>
-      <c r="R50" s="9"/>
-      <c r="S50" s="9"/>
-      <c r="T50" s="9"/>
-      <c r="U50" s="9"/>
+      <c r="Q50" s="36"/>
+      <c r="R50" s="28"/>
+      <c r="S50" s="36"/>
+      <c r="T50" s="36"/>
+      <c r="U50" s="36"/>
       <c r="V50" s="9"/>
       <c r="W50" s="9"/>
       <c r="X50" s="9"/>
@@ -14414,11 +14476,11 @@
       <c r="N51" s="9"/>
       <c r="O51" s="9"/>
       <c r="P51" s="9"/>
-      <c r="Q51" s="9"/>
-      <c r="R51" s="9"/>
-      <c r="S51" s="9"/>
-      <c r="T51" s="9"/>
-      <c r="U51" s="9"/>
+      <c r="Q51" s="36"/>
+      <c r="R51" s="28"/>
+      <c r="S51" s="36"/>
+      <c r="T51" s="36"/>
+      <c r="U51" s="36"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
       <c r="X51" s="9"/>
@@ -14478,11 +14540,11 @@
       <c r="N52" s="9"/>
       <c r="O52" s="9"/>
       <c r="P52" s="9"/>
-      <c r="Q52" s="9"/>
-      <c r="R52" s="9"/>
-      <c r="S52" s="9"/>
-      <c r="T52" s="9"/>
-      <c r="U52" s="9"/>
+      <c r="Q52" s="36"/>
+      <c r="R52" s="28"/>
+      <c r="S52" s="36"/>
+      <c r="T52" s="36"/>
+      <c r="U52" s="36"/>
       <c r="V52" s="9"/>
       <c r="W52" s="9"/>
       <c r="X52" s="9"/>
@@ -14542,11 +14604,11 @@
       <c r="N53" s="9"/>
       <c r="O53" s="9"/>
       <c r="P53" s="9"/>
-      <c r="Q53" s="9"/>
-      <c r="R53" s="9"/>
-      <c r="S53" s="9"/>
-      <c r="T53" s="9"/>
-      <c r="U53" s="9"/>
+      <c r="Q53" s="36"/>
+      <c r="R53" s="28"/>
+      <c r="S53" s="36"/>
+      <c r="T53" s="36"/>
+      <c r="U53" s="36"/>
       <c r="V53" s="9"/>
       <c r="W53" s="9"/>
       <c r="X53" s="9"/>
@@ -14606,11 +14668,11 @@
       <c r="N54" s="9"/>
       <c r="O54" s="9"/>
       <c r="P54" s="9"/>
-      <c r="Q54" s="9"/>
-      <c r="R54" s="9"/>
-      <c r="S54" s="9"/>
-      <c r="T54" s="9"/>
-      <c r="U54" s="9"/>
+      <c r="Q54" s="36"/>
+      <c r="R54" s="28"/>
+      <c r="S54" s="36"/>
+      <c r="T54" s="36"/>
+      <c r="U54" s="36"/>
       <c r="V54" s="9"/>
       <c r="W54" s="9"/>
       <c r="X54" s="9"/>
@@ -14670,11 +14732,11 @@
       <c r="N55" s="9"/>
       <c r="O55" s="9"/>
       <c r="P55" s="9"/>
-      <c r="Q55" s="9"/>
-      <c r="R55" s="9"/>
-      <c r="S55" s="9"/>
-      <c r="T55" s="9"/>
-      <c r="U55" s="9"/>
+      <c r="Q55" s="36"/>
+      <c r="R55" s="28"/>
+      <c r="S55" s="36"/>
+      <c r="T55" s="36"/>
+      <c r="U55" s="36"/>
       <c r="V55" s="9"/>
       <c r="W55" s="9"/>
       <c r="X55" s="9"/>
@@ -14734,11 +14796,11 @@
       <c r="N56" s="9"/>
       <c r="O56" s="9"/>
       <c r="P56" s="9"/>
-      <c r="Q56" s="9"/>
-      <c r="R56" s="9"/>
-      <c r="S56" s="9"/>
-      <c r="T56" s="9"/>
-      <c r="U56" s="9"/>
+      <c r="Q56" s="36"/>
+      <c r="R56" s="28"/>
+      <c r="S56" s="36"/>
+      <c r="T56" s="36"/>
+      <c r="U56" s="36"/>
       <c r="V56" s="9"/>
       <c r="W56" s="9"/>
       <c r="X56" s="9"/>
@@ -14798,11 +14860,11 @@
       <c r="N57" s="9"/>
       <c r="O57" s="9"/>
       <c r="P57" s="9"/>
-      <c r="Q57" s="9"/>
-      <c r="R57" s="9"/>
-      <c r="S57" s="9"/>
-      <c r="T57" s="9"/>
-      <c r="U57" s="9"/>
+      <c r="Q57" s="36"/>
+      <c r="R57" s="28"/>
+      <c r="S57" s="36"/>
+      <c r="T57" s="36"/>
+      <c r="U57" s="36"/>
       <c r="V57" s="9"/>
       <c r="W57" s="9"/>
       <c r="X57" s="9"/>
@@ -14862,11 +14924,11 @@
       <c r="N58" s="9"/>
       <c r="O58" s="9"/>
       <c r="P58" s="9"/>
-      <c r="Q58" s="9"/>
-      <c r="R58" s="9"/>
-      <c r="S58" s="9"/>
-      <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
+      <c r="Q58" s="36"/>
+      <c r="R58" s="28"/>
+      <c r="S58" s="36"/>
+      <c r="T58" s="36"/>
+      <c r="U58" s="36"/>
       <c r="V58" s="9"/>
       <c r="W58" s="9"/>
       <c r="X58" s="9"/>
@@ -14926,11 +14988,11 @@
       <c r="N59" s="9"/>
       <c r="O59" s="9"/>
       <c r="P59" s="9"/>
-      <c r="Q59" s="9"/>
-      <c r="R59" s="9"/>
-      <c r="S59" s="9"/>
-      <c r="T59" s="9"/>
-      <c r="U59" s="9"/>
+      <c r="Q59" s="36"/>
+      <c r="R59" s="28"/>
+      <c r="S59" s="36"/>
+      <c r="T59" s="36"/>
+      <c r="U59" s="36"/>
       <c r="V59" s="9"/>
       <c r="W59" s="9"/>
       <c r="X59" s="9"/>
@@ -14990,11 +15052,11 @@
       <c r="N60" s="9"/>
       <c r="O60" s="9"/>
       <c r="P60" s="9"/>
-      <c r="Q60" s="9"/>
-      <c r="R60" s="9"/>
-      <c r="S60" s="9"/>
-      <c r="T60" s="9"/>
-      <c r="U60" s="9"/>
+      <c r="Q60" s="36"/>
+      <c r="R60" s="28"/>
+      <c r="S60" s="36"/>
+      <c r="T60" s="36"/>
+      <c r="U60" s="36"/>
       <c r="V60" s="9"/>
       <c r="W60" s="9"/>
       <c r="X60" s="9"/>
@@ -15054,11 +15116,11 @@
       <c r="N61" s="9"/>
       <c r="O61" s="9"/>
       <c r="P61" s="9"/>
-      <c r="Q61" s="9"/>
-      <c r="R61" s="9"/>
-      <c r="S61" s="9"/>
-      <c r="T61" s="9"/>
-      <c r="U61" s="9"/>
+      <c r="Q61" s="36"/>
+      <c r="R61" s="28"/>
+      <c r="S61" s="36"/>
+      <c r="T61" s="36"/>
+      <c r="U61" s="36"/>
       <c r="V61" s="9"/>
       <c r="W61" s="9"/>
       <c r="X61" s="9"/>
@@ -15118,11 +15180,11 @@
       <c r="N62" s="9"/>
       <c r="O62" s="9"/>
       <c r="P62" s="9"/>
-      <c r="Q62" s="9"/>
-      <c r="R62" s="9"/>
-      <c r="S62" s="9"/>
-      <c r="T62" s="9"/>
-      <c r="U62" s="9"/>
+      <c r="Q62" s="36"/>
+      <c r="R62" s="28"/>
+      <c r="S62" s="36"/>
+      <c r="T62" s="36"/>
+      <c r="U62" s="36"/>
       <c r="V62" s="9"/>
       <c r="W62" s="9"/>
       <c r="X62" s="9"/>
@@ -15182,11 +15244,11 @@
       <c r="N63" s="9"/>
       <c r="O63" s="9"/>
       <c r="P63" s="9"/>
-      <c r="Q63" s="9"/>
-      <c r="R63" s="9"/>
-      <c r="S63" s="9"/>
-      <c r="T63" s="9"/>
-      <c r="U63" s="9"/>
+      <c r="Q63" s="36"/>
+      <c r="R63" s="28"/>
+      <c r="S63" s="36"/>
+      <c r="T63" s="36"/>
+      <c r="U63" s="36"/>
       <c r="V63" s="9"/>
       <c r="W63" s="9"/>
       <c r="X63" s="9"/>
@@ -15246,11 +15308,11 @@
       <c r="N64" s="9"/>
       <c r="O64" s="9"/>
       <c r="P64" s="9"/>
-      <c r="Q64" s="9"/>
-      <c r="R64" s="9"/>
-      <c r="S64" s="9"/>
-      <c r="T64" s="9"/>
-      <c r="U64" s="9"/>
+      <c r="Q64" s="36"/>
+      <c r="R64" s="28"/>
+      <c r="S64" s="36"/>
+      <c r="T64" s="36"/>
+      <c r="U64" s="36"/>
       <c r="V64" s="9"/>
       <c r="W64" s="9"/>
       <c r="X64" s="9"/>
@@ -15310,11 +15372,11 @@
       <c r="N65" s="9"/>
       <c r="O65" s="9"/>
       <c r="P65" s="9"/>
-      <c r="Q65" s="9"/>
-      <c r="R65" s="9"/>
-      <c r="S65" s="9"/>
-      <c r="T65" s="9"/>
-      <c r="U65" s="9"/>
+      <c r="Q65" s="36"/>
+      <c r="R65" s="28"/>
+      <c r="S65" s="36"/>
+      <c r="T65" s="36"/>
+      <c r="U65" s="36"/>
       <c r="V65" s="9"/>
       <c r="W65" s="9"/>
       <c r="X65" s="9"/>
@@ -15374,11 +15436,11 @@
       <c r="N66" s="9"/>
       <c r="O66" s="9"/>
       <c r="P66" s="9"/>
-      <c r="Q66" s="9"/>
-      <c r="R66" s="9"/>
-      <c r="S66" s="9"/>
-      <c r="T66" s="9"/>
-      <c r="U66" s="9"/>
+      <c r="Q66" s="36"/>
+      <c r="R66" s="28"/>
+      <c r="S66" s="36"/>
+      <c r="T66" s="36"/>
+      <c r="U66" s="36"/>
       <c r="V66" s="9"/>
       <c r="W66" s="9"/>
       <c r="X66" s="9"/>
@@ -15438,11 +15500,11 @@
       <c r="N67" s="9"/>
       <c r="O67" s="9"/>
       <c r="P67" s="9"/>
-      <c r="Q67" s="9"/>
-      <c r="R67" s="9"/>
-      <c r="S67" s="9"/>
-      <c r="T67" s="9"/>
-      <c r="U67" s="9"/>
+      <c r="Q67" s="36"/>
+      <c r="R67" s="28"/>
+      <c r="S67" s="36"/>
+      <c r="T67" s="36"/>
+      <c r="U67" s="36"/>
       <c r="V67" s="9"/>
       <c r="W67" s="9"/>
       <c r="X67" s="9"/>
@@ -15502,11 +15564,11 @@
       <c r="N68" s="9"/>
       <c r="O68" s="9"/>
       <c r="P68" s="9"/>
-      <c r="Q68" s="9"/>
-      <c r="R68" s="9"/>
-      <c r="S68" s="9"/>
-      <c r="T68" s="9"/>
-      <c r="U68" s="9"/>
+      <c r="Q68" s="36"/>
+      <c r="R68" s="28"/>
+      <c r="S68" s="36"/>
+      <c r="T68" s="36"/>
+      <c r="U68" s="36"/>
       <c r="V68" s="9"/>
       <c r="W68" s="9"/>
       <c r="X68" s="9"/>
@@ -15566,11 +15628,11 @@
       <c r="N69" s="9"/>
       <c r="O69" s="9"/>
       <c r="P69" s="9"/>
-      <c r="Q69" s="9"/>
-      <c r="R69" s="9"/>
-      <c r="S69" s="9"/>
-      <c r="T69" s="9"/>
-      <c r="U69" s="9"/>
+      <c r="Q69" s="36"/>
+      <c r="R69" s="28"/>
+      <c r="S69" s="36"/>
+      <c r="T69" s="36"/>
+      <c r="U69" s="36"/>
       <c r="V69" s="9"/>
       <c r="W69" s="9"/>
       <c r="X69" s="9"/>
@@ -15630,11 +15692,11 @@
       <c r="N70" s="9"/>
       <c r="O70" s="9"/>
       <c r="P70" s="9"/>
-      <c r="Q70" s="9"/>
-      <c r="R70" s="9"/>
-      <c r="S70" s="9"/>
-      <c r="T70" s="9"/>
-      <c r="U70" s="9"/>
+      <c r="Q70" s="36"/>
+      <c r="R70" s="28"/>
+      <c r="S70" s="36"/>
+      <c r="T70" s="36"/>
+      <c r="U70" s="36"/>
       <c r="V70" s="9"/>
       <c r="W70" s="9"/>
       <c r="X70" s="9"/>
@@ -15694,11 +15756,11 @@
       <c r="N71" s="9"/>
       <c r="O71" s="9"/>
       <c r="P71" s="9"/>
-      <c r="Q71" s="9"/>
-      <c r="R71" s="9"/>
-      <c r="S71" s="9"/>
-      <c r="T71" s="9"/>
-      <c r="U71" s="9"/>
+      <c r="Q71" s="36"/>
+      <c r="R71" s="28"/>
+      <c r="S71" s="36"/>
+      <c r="T71" s="36"/>
+      <c r="U71" s="36"/>
       <c r="V71" s="9"/>
       <c r="W71" s="9"/>
       <c r="X71" s="9"/>
@@ -15758,11 +15820,11 @@
       <c r="N72" s="9"/>
       <c r="O72" s="9"/>
       <c r="P72" s="9"/>
-      <c r="Q72" s="9"/>
-      <c r="R72" s="9"/>
-      <c r="S72" s="9"/>
-      <c r="T72" s="9"/>
-      <c r="U72" s="9"/>
+      <c r="Q72" s="36"/>
+      <c r="R72" s="28"/>
+      <c r="S72" s="36"/>
+      <c r="T72" s="36"/>
+      <c r="U72" s="36"/>
       <c r="V72" s="9"/>
       <c r="W72" s="9"/>
       <c r="X72" s="9"/>
@@ -15822,11 +15884,11 @@
       <c r="N73" s="9"/>
       <c r="O73" s="9"/>
       <c r="P73" s="9"/>
-      <c r="Q73" s="9"/>
-      <c r="R73" s="9"/>
-      <c r="S73" s="9"/>
-      <c r="T73" s="9"/>
-      <c r="U73" s="9"/>
+      <c r="Q73" s="36"/>
+      <c r="R73" s="28"/>
+      <c r="S73" s="36"/>
+      <c r="T73" s="36"/>
+      <c r="U73" s="36"/>
       <c r="V73" s="9"/>
       <c r="W73" s="9"/>
       <c r="X73" s="9"/>
@@ -15886,11 +15948,11 @@
       <c r="N74" s="9"/>
       <c r="O74" s="9"/>
       <c r="P74" s="9"/>
-      <c r="Q74" s="9"/>
-      <c r="R74" s="9"/>
-      <c r="S74" s="9"/>
-      <c r="T74" s="9"/>
-      <c r="U74" s="9"/>
+      <c r="Q74" s="36"/>
+      <c r="R74" s="28"/>
+      <c r="S74" s="36"/>
+      <c r="T74" s="36"/>
+      <c r="U74" s="36"/>
       <c r="V74" s="9"/>
       <c r="W74" s="9"/>
       <c r="X74" s="9"/>
@@ -15950,11 +16012,11 @@
       <c r="N75" s="9"/>
       <c r="O75" s="9"/>
       <c r="P75" s="9"/>
-      <c r="Q75" s="9"/>
-      <c r="R75" s="9"/>
-      <c r="S75" s="9"/>
-      <c r="T75" s="9"/>
-      <c r="U75" s="9"/>
+      <c r="Q75" s="36"/>
+      <c r="R75" s="28"/>
+      <c r="S75" s="36"/>
+      <c r="T75" s="36"/>
+      <c r="U75" s="36"/>
       <c r="V75" s="9"/>
       <c r="W75" s="9"/>
       <c r="X75" s="9"/>
@@ -16014,11 +16076,11 @@
       <c r="N76" s="9"/>
       <c r="O76" s="9"/>
       <c r="P76" s="9"/>
-      <c r="Q76" s="9"/>
-      <c r="R76" s="9"/>
-      <c r="S76" s="9"/>
-      <c r="T76" s="9"/>
-      <c r="U76" s="9"/>
+      <c r="Q76" s="36"/>
+      <c r="R76" s="28"/>
+      <c r="S76" s="36"/>
+      <c r="T76" s="36"/>
+      <c r="U76" s="36"/>
       <c r="V76" s="9"/>
       <c r="W76" s="9"/>
       <c r="X76" s="9"/>
@@ -16078,11 +16140,11 @@
       <c r="N77" s="9"/>
       <c r="O77" s="9"/>
       <c r="P77" s="9"/>
-      <c r="Q77" s="9"/>
-      <c r="R77" s="9"/>
-      <c r="S77" s="9"/>
-      <c r="T77" s="9"/>
-      <c r="U77" s="9"/>
+      <c r="Q77" s="36"/>
+      <c r="R77" s="28"/>
+      <c r="S77" s="36"/>
+      <c r="T77" s="36"/>
+      <c r="U77" s="36"/>
       <c r="V77" s="9"/>
       <c r="W77" s="9"/>
       <c r="X77" s="9"/>
@@ -16142,11 +16204,11 @@
       <c r="N78" s="9"/>
       <c r="O78" s="9"/>
       <c r="P78" s="9"/>
-      <c r="Q78" s="9"/>
-      <c r="R78" s="9"/>
-      <c r="S78" s="9"/>
-      <c r="T78" s="9"/>
-      <c r="U78" s="9"/>
+      <c r="Q78" s="36"/>
+      <c r="R78" s="28"/>
+      <c r="S78" s="36"/>
+      <c r="T78" s="36"/>
+      <c r="U78" s="36"/>
       <c r="V78" s="9"/>
       <c r="W78" s="9"/>
       <c r="X78" s="9"/>
@@ -16206,11 +16268,11 @@
       <c r="N79" s="9"/>
       <c r="O79" s="9"/>
       <c r="P79" s="9"/>
-      <c r="Q79" s="9"/>
-      <c r="R79" s="9"/>
-      <c r="S79" s="9"/>
-      <c r="T79" s="9"/>
-      <c r="U79" s="9"/>
+      <c r="Q79" s="36"/>
+      <c r="R79" s="28"/>
+      <c r="S79" s="36"/>
+      <c r="T79" s="36"/>
+      <c r="U79" s="36"/>
       <c r="V79" s="9"/>
       <c r="W79" s="9"/>
       <c r="X79" s="9"/>
@@ -16270,11 +16332,11 @@
       <c r="N80" s="9"/>
       <c r="O80" s="9"/>
       <c r="P80" s="9"/>
-      <c r="Q80" s="9"/>
-      <c r="R80" s="9"/>
-      <c r="S80" s="9"/>
-      <c r="T80" s="9"/>
-      <c r="U80" s="9"/>
+      <c r="Q80" s="36"/>
+      <c r="R80" s="28"/>
+      <c r="S80" s="36"/>
+      <c r="T80" s="36"/>
+      <c r="U80" s="36"/>
       <c r="V80" s="9"/>
       <c r="W80" s="9"/>
       <c r="X80" s="9"/>
@@ -16334,11 +16396,11 @@
       <c r="N81" s="9"/>
       <c r="O81" s="9"/>
       <c r="P81" s="9"/>
-      <c r="Q81" s="9"/>
-      <c r="R81" s="9"/>
-      <c r="S81" s="9"/>
-      <c r="T81" s="9"/>
-      <c r="U81" s="9"/>
+      <c r="Q81" s="36"/>
+      <c r="R81" s="28"/>
+      <c r="S81" s="36"/>
+      <c r="T81" s="36"/>
+      <c r="U81" s="36"/>
       <c r="V81" s="9"/>
       <c r="W81" s="9"/>
       <c r="X81" s="9"/>
@@ -16398,11 +16460,11 @@
       <c r="N82" s="9"/>
       <c r="O82" s="9"/>
       <c r="P82" s="9"/>
-      <c r="Q82" s="9"/>
-      <c r="R82" s="9"/>
-      <c r="S82" s="9"/>
-      <c r="T82" s="9"/>
-      <c r="U82" s="9"/>
+      <c r="Q82" s="36"/>
+      <c r="R82" s="28"/>
+      <c r="S82" s="36"/>
+      <c r="T82" s="36"/>
+      <c r="U82" s="36"/>
       <c r="V82" s="9"/>
       <c r="W82" s="9"/>
       <c r="X82" s="9"/>
@@ -16462,11 +16524,11 @@
       <c r="N83" s="9"/>
       <c r="O83" s="9"/>
       <c r="P83" s="9"/>
-      <c r="Q83" s="9"/>
-      <c r="R83" s="9"/>
-      <c r="S83" s="9"/>
-      <c r="T83" s="9"/>
-      <c r="U83" s="9"/>
+      <c r="Q83" s="36"/>
+      <c r="R83" s="28"/>
+      <c r="S83" s="36"/>
+      <c r="T83" s="36"/>
+      <c r="U83" s="36"/>
       <c r="V83" s="9"/>
       <c r="W83" s="9"/>
       <c r="X83" s="9"/>
@@ -16526,11 +16588,11 @@
       <c r="N84" s="9"/>
       <c r="O84" s="9"/>
       <c r="P84" s="9"/>
-      <c r="Q84" s="9"/>
-      <c r="R84" s="9"/>
-      <c r="S84" s="9"/>
-      <c r="T84" s="9"/>
-      <c r="U84" s="9"/>
+      <c r="Q84" s="36"/>
+      <c r="R84" s="28"/>
+      <c r="S84" s="36"/>
+      <c r="T84" s="36"/>
+      <c r="U84" s="36"/>
       <c r="V84" s="9"/>
       <c r="W84" s="9"/>
       <c r="X84" s="9"/>
@@ -16590,11 +16652,11 @@
       <c r="N85" s="9"/>
       <c r="O85" s="9"/>
       <c r="P85" s="9"/>
-      <c r="Q85" s="9"/>
-      <c r="R85" s="9"/>
-      <c r="S85" s="9"/>
-      <c r="T85" s="9"/>
-      <c r="U85" s="9"/>
+      <c r="Q85" s="36"/>
+      <c r="R85" s="28"/>
+      <c r="S85" s="36"/>
+      <c r="T85" s="36"/>
+      <c r="U85" s="36"/>
       <c r="V85" s="9"/>
       <c r="W85" s="9"/>
       <c r="X85" s="9"/>
@@ -16654,11 +16716,11 @@
       <c r="N86" s="9"/>
       <c r="O86" s="9"/>
       <c r="P86" s="9"/>
-      <c r="Q86" s="9"/>
-      <c r="R86" s="9"/>
-      <c r="S86" s="9"/>
-      <c r="T86" s="9"/>
-      <c r="U86" s="9"/>
+      <c r="Q86" s="36"/>
+      <c r="R86" s="28"/>
+      <c r="S86" s="36"/>
+      <c r="T86" s="36"/>
+      <c r="U86" s="36"/>
       <c r="V86" s="9"/>
       <c r="W86" s="9"/>
       <c r="X86" s="9"/>
@@ -16718,11 +16780,11 @@
       <c r="N87" s="9"/>
       <c r="O87" s="9"/>
       <c r="P87" s="9"/>
-      <c r="Q87" s="9"/>
-      <c r="R87" s="9"/>
-      <c r="S87" s="9"/>
-      <c r="T87" s="9"/>
-      <c r="U87" s="9"/>
+      <c r="Q87" s="36"/>
+      <c r="R87" s="28"/>
+      <c r="S87" s="36"/>
+      <c r="T87" s="36"/>
+      <c r="U87" s="36"/>
       <c r="V87" s="9"/>
       <c r="W87" s="9"/>
       <c r="X87" s="9"/>
@@ -16782,11 +16844,11 @@
       <c r="N88" s="9"/>
       <c r="O88" s="9"/>
       <c r="P88" s="9"/>
-      <c r="Q88" s="9"/>
-      <c r="R88" s="9"/>
-      <c r="S88" s="9"/>
-      <c r="T88" s="9"/>
-      <c r="U88" s="9"/>
+      <c r="Q88" s="36"/>
+      <c r="R88" s="28"/>
+      <c r="S88" s="36"/>
+      <c r="T88" s="36"/>
+      <c r="U88" s="36"/>
       <c r="V88" s="9"/>
       <c r="W88" s="9"/>
       <c r="X88" s="9"/>
@@ -16846,11 +16908,11 @@
       <c r="N89" s="9"/>
       <c r="O89" s="9"/>
       <c r="P89" s="9"/>
-      <c r="Q89" s="9"/>
-      <c r="R89" s="9"/>
-      <c r="S89" s="9"/>
-      <c r="T89" s="9"/>
-      <c r="U89" s="9"/>
+      <c r="Q89" s="36"/>
+      <c r="R89" s="28"/>
+      <c r="S89" s="36"/>
+      <c r="T89" s="36"/>
+      <c r="U89" s="36"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
       <c r="X89" s="9"/>
@@ -16910,11 +16972,11 @@
       <c r="N90" s="9"/>
       <c r="O90" s="9"/>
       <c r="P90" s="9"/>
-      <c r="Q90" s="9"/>
-      <c r="R90" s="9"/>
-      <c r="S90" s="9"/>
-      <c r="T90" s="9"/>
-      <c r="U90" s="9"/>
+      <c r="Q90" s="36"/>
+      <c r="R90" s="28"/>
+      <c r="S90" s="36"/>
+      <c r="T90" s="36"/>
+      <c r="U90" s="36"/>
       <c r="V90" s="9"/>
       <c r="W90" s="9"/>
       <c r="X90" s="9"/>
@@ -16974,11 +17036,11 @@
       <c r="N91" s="9"/>
       <c r="O91" s="9"/>
       <c r="P91" s="9"/>
-      <c r="Q91" s="9"/>
-      <c r="R91" s="9"/>
-      <c r="S91" s="9"/>
-      <c r="T91" s="9"/>
-      <c r="U91" s="9"/>
+      <c r="Q91" s="36"/>
+      <c r="R91" s="28"/>
+      <c r="S91" s="36"/>
+      <c r="T91" s="36"/>
+      <c r="U91" s="36"/>
       <c r="V91" s="9"/>
       <c r="W91" s="9"/>
       <c r="X91" s="9"/>
@@ -17038,11 +17100,11 @@
       <c r="N92" s="9"/>
       <c r="O92" s="9"/>
       <c r="P92" s="9"/>
-      <c r="Q92" s="9"/>
-      <c r="R92" s="9"/>
-      <c r="S92" s="9"/>
-      <c r="T92" s="9"/>
-      <c r="U92" s="9"/>
+      <c r="Q92" s="36"/>
+      <c r="R92" s="28"/>
+      <c r="S92" s="36"/>
+      <c r="T92" s="36"/>
+      <c r="U92" s="36"/>
       <c r="V92" s="9"/>
       <c r="W92" s="9"/>
       <c r="X92" s="9"/>
@@ -17102,11 +17164,11 @@
       <c r="N93" s="9"/>
       <c r="O93" s="9"/>
       <c r="P93" s="9"/>
-      <c r="Q93" s="9"/>
-      <c r="R93" s="9"/>
-      <c r="S93" s="9"/>
-      <c r="T93" s="9"/>
-      <c r="U93" s="9"/>
+      <c r="Q93" s="36"/>
+      <c r="R93" s="28"/>
+      <c r="S93" s="36"/>
+      <c r="T93" s="36"/>
+      <c r="U93" s="36"/>
       <c r="V93" s="9"/>
       <c r="W93" s="9"/>
       <c r="X93" s="9"/>
@@ -17166,11 +17228,11 @@
       <c r="N94" s="9"/>
       <c r="O94" s="9"/>
       <c r="P94" s="9"/>
-      <c r="Q94" s="9"/>
-      <c r="R94" s="9"/>
-      <c r="S94" s="9"/>
-      <c r="T94" s="9"/>
-      <c r="U94" s="9"/>
+      <c r="Q94" s="36"/>
+      <c r="R94" s="28"/>
+      <c r="S94" s="36"/>
+      <c r="T94" s="36"/>
+      <c r="U94" s="36"/>
       <c r="V94" s="9"/>
       <c r="W94" s="9"/>
       <c r="X94" s="9"/>
@@ -17230,11 +17292,11 @@
       <c r="N95" s="9"/>
       <c r="O95" s="9"/>
       <c r="P95" s="9"/>
-      <c r="Q95" s="9"/>
-      <c r="R95" s="9"/>
-      <c r="S95" s="9"/>
-      <c r="T95" s="9"/>
-      <c r="U95" s="9"/>
+      <c r="Q95" s="36"/>
+      <c r="R95" s="28"/>
+      <c r="S95" s="36"/>
+      <c r="T95" s="36"/>
+      <c r="U95" s="36"/>
       <c r="V95" s="9"/>
       <c r="W95" s="9"/>
       <c r="X95" s="9"/>
@@ -17294,11 +17356,11 @@
       <c r="N96" s="9"/>
       <c r="O96" s="9"/>
       <c r="P96" s="9"/>
-      <c r="Q96" s="9"/>
-      <c r="R96" s="9"/>
-      <c r="S96" s="9"/>
-      <c r="T96" s="9"/>
-      <c r="U96" s="9"/>
+      <c r="Q96" s="36"/>
+      <c r="R96" s="28"/>
+      <c r="S96" s="36"/>
+      <c r="T96" s="36"/>
+      <c r="U96" s="36"/>
       <c r="V96" s="9"/>
       <c r="W96" s="9"/>
       <c r="X96" s="9"/>
@@ -17358,11 +17420,11 @@
       <c r="N97" s="9"/>
       <c r="O97" s="9"/>
       <c r="P97" s="9"/>
-      <c r="Q97" s="9"/>
-      <c r="R97" s="9"/>
-      <c r="S97" s="9"/>
-      <c r="T97" s="9"/>
-      <c r="U97" s="9"/>
+      <c r="Q97" s="36"/>
+      <c r="R97" s="28"/>
+      <c r="S97" s="36"/>
+      <c r="T97" s="36"/>
+      <c r="U97" s="36"/>
       <c r="V97" s="9"/>
       <c r="W97" s="9"/>
       <c r="X97" s="9"/>
@@ -17422,11 +17484,11 @@
       <c r="N98" s="9"/>
       <c r="O98" s="9"/>
       <c r="P98" s="9"/>
-      <c r="Q98" s="9"/>
-      <c r="R98" s="9"/>
-      <c r="S98" s="9"/>
-      <c r="T98" s="9"/>
-      <c r="U98" s="9"/>
+      <c r="Q98" s="36"/>
+      <c r="R98" s="28"/>
+      <c r="S98" s="36"/>
+      <c r="T98" s="36"/>
+      <c r="U98" s="36"/>
       <c r="V98" s="9"/>
       <c r="W98" s="9"/>
       <c r="X98" s="9"/>
@@ -17486,11 +17548,11 @@
       <c r="N99" s="9"/>
       <c r="O99" s="9"/>
       <c r="P99" s="9"/>
-      <c r="Q99" s="9"/>
-      <c r="R99" s="9"/>
-      <c r="S99" s="9"/>
-      <c r="T99" s="9"/>
-      <c r="U99" s="9"/>
+      <c r="Q99" s="36"/>
+      <c r="R99" s="28"/>
+      <c r="S99" s="36"/>
+      <c r="T99" s="36"/>
+      <c r="U99" s="36"/>
       <c r="V99" s="9"/>
       <c r="W99" s="9"/>
       <c r="X99" s="9"/>
@@ -17550,11 +17612,11 @@
       <c r="N100" s="9"/>
       <c r="O100" s="9"/>
       <c r="P100" s="9"/>
-      <c r="Q100" s="9"/>
-      <c r="R100" s="9"/>
-      <c r="S100" s="9"/>
-      <c r="T100" s="9"/>
-      <c r="U100" s="9"/>
+      <c r="Q100" s="36"/>
+      <c r="R100" s="28"/>
+      <c r="S100" s="36"/>
+      <c r="T100" s="36"/>
+      <c r="U100" s="36"/>
       <c r="V100" s="9"/>
       <c r="W100" s="9"/>
       <c r="X100" s="9"/>
@@ -17614,11 +17676,11 @@
       <c r="N101" s="9"/>
       <c r="O101" s="9"/>
       <c r="P101" s="9"/>
-      <c r="Q101" s="9"/>
-      <c r="R101" s="9"/>
-      <c r="S101" s="9"/>
-      <c r="T101" s="9"/>
-      <c r="U101" s="9"/>
+      <c r="Q101" s="36"/>
+      <c r="R101" s="28"/>
+      <c r="S101" s="36"/>
+      <c r="T101" s="36"/>
+      <c r="U101" s="36"/>
       <c r="V101" s="9"/>
       <c r="W101" s="9"/>
       <c r="X101" s="9"/>
@@ -17678,11 +17740,11 @@
       <c r="N102" s="9"/>
       <c r="O102" s="9"/>
       <c r="P102" s="9"/>
-      <c r="Q102" s="9"/>
-      <c r="R102" s="9"/>
-      <c r="S102" s="9"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
+      <c r="Q102" s="36"/>
+      <c r="R102" s="28"/>
+      <c r="S102" s="36"/>
+      <c r="T102" s="36"/>
+      <c r="U102" s="36"/>
       <c r="V102" s="9"/>
       <c r="W102" s="9"/>
       <c r="X102" s="9"/>
@@ -17742,11 +17804,11 @@
       <c r="N103" s="9"/>
       <c r="O103" s="9"/>
       <c r="P103" s="9"/>
-      <c r="Q103" s="9"/>
-      <c r="R103" s="9"/>
-      <c r="S103" s="9"/>
-      <c r="T103" s="9"/>
-      <c r="U103" s="9"/>
+      <c r="Q103" s="36"/>
+      <c r="R103" s="28"/>
+      <c r="S103" s="36"/>
+      <c r="T103" s="36"/>
+      <c r="U103" s="36"/>
       <c r="V103" s="9"/>
       <c r="W103" s="9"/>
       <c r="X103" s="9"/>
@@ -17806,11 +17868,11 @@
       <c r="N104" s="9"/>
       <c r="O104" s="9"/>
       <c r="P104" s="9"/>
-      <c r="Q104" s="9"/>
-      <c r="R104" s="9"/>
-      <c r="S104" s="9"/>
-      <c r="T104" s="9"/>
-      <c r="U104" s="9"/>
+      <c r="Q104" s="36"/>
+      <c r="R104" s="28"/>
+      <c r="S104" s="36"/>
+      <c r="T104" s="36"/>
+      <c r="U104" s="36"/>
       <c r="V104" s="9"/>
       <c r="W104" s="9"/>
       <c r="X104" s="9"/>
@@ -17870,11 +17932,11 @@
       <c r="N105" s="9"/>
       <c r="O105" s="9"/>
       <c r="P105" s="9"/>
-      <c r="Q105" s="9"/>
-      <c r="R105" s="9"/>
-      <c r="S105" s="9"/>
-      <c r="T105" s="9"/>
-      <c r="U105" s="9"/>
+      <c r="Q105" s="36"/>
+      <c r="R105" s="28"/>
+      <c r="S105" s="36"/>
+      <c r="T105" s="36"/>
+      <c r="U105" s="36"/>
       <c r="V105" s="9"/>
       <c r="W105" s="9"/>
       <c r="X105" s="9"/>
@@ -17934,11 +17996,11 @@
       <c r="N106" s="9"/>
       <c r="O106" s="9"/>
       <c r="P106" s="9"/>
-      <c r="Q106" s="9"/>
-      <c r="R106" s="9"/>
-      <c r="S106" s="9"/>
-      <c r="T106" s="9"/>
-      <c r="U106" s="9"/>
+      <c r="Q106" s="36"/>
+      <c r="R106" s="28"/>
+      <c r="S106" s="36"/>
+      <c r="T106" s="36"/>
+      <c r="U106" s="36"/>
       <c r="V106" s="9"/>
       <c r="W106" s="9"/>
       <c r="X106" s="9"/>
@@ -17998,11 +18060,11 @@
       <c r="N107" s="9"/>
       <c r="O107" s="9"/>
       <c r="P107" s="9"/>
-      <c r="Q107" s="9"/>
-      <c r="R107" s="9"/>
-      <c r="S107" s="9"/>
-      <c r="T107" s="9"/>
-      <c r="U107" s="9"/>
+      <c r="Q107" s="36"/>
+      <c r="R107" s="28"/>
+      <c r="S107" s="36"/>
+      <c r="T107" s="36"/>
+      <c r="U107" s="36"/>
       <c r="V107" s="9"/>
       <c r="W107" s="9"/>
       <c r="X107" s="9"/>
@@ -18062,11 +18124,11 @@
       <c r="N108" s="9"/>
       <c r="O108" s="9"/>
       <c r="P108" s="9"/>
-      <c r="Q108" s="9"/>
-      <c r="R108" s="9"/>
-      <c r="S108" s="9"/>
-      <c r="T108" s="9"/>
-      <c r="U108" s="9"/>
+      <c r="Q108" s="36"/>
+      <c r="R108" s="28"/>
+      <c r="S108" s="36"/>
+      <c r="T108" s="36"/>
+      <c r="U108" s="36"/>
       <c r="V108" s="9"/>
       <c r="W108" s="9"/>
       <c r="X108" s="9"/>
@@ -18126,11 +18188,11 @@
       <c r="N109" s="9"/>
       <c r="O109" s="9"/>
       <c r="P109" s="9"/>
-      <c r="Q109" s="9"/>
-      <c r="R109" s="9"/>
-      <c r="S109" s="9"/>
-      <c r="T109" s="9"/>
-      <c r="U109" s="9"/>
+      <c r="Q109" s="36"/>
+      <c r="R109" s="28"/>
+      <c r="S109" s="36"/>
+      <c r="T109" s="36"/>
+      <c r="U109" s="36"/>
       <c r="V109" s="9"/>
       <c r="W109" s="9"/>
       <c r="X109" s="9"/>
@@ -18190,11 +18252,11 @@
       <c r="N110" s="9"/>
       <c r="O110" s="9"/>
       <c r="P110" s="9"/>
-      <c r="Q110" s="9"/>
-      <c r="R110" s="9"/>
-      <c r="S110" s="9"/>
-      <c r="T110" s="9"/>
-      <c r="U110" s="9"/>
+      <c r="Q110" s="36"/>
+      <c r="R110" s="28"/>
+      <c r="S110" s="36"/>
+      <c r="T110" s="36"/>
+      <c r="U110" s="36"/>
       <c r="V110" s="9"/>
       <c r="W110" s="9"/>
       <c r="X110" s="9"/>
@@ -18254,11 +18316,11 @@
       <c r="N111" s="9"/>
       <c r="O111" s="9"/>
       <c r="P111" s="9"/>
-      <c r="Q111" s="9"/>
-      <c r="R111" s="9"/>
-      <c r="S111" s="9"/>
-      <c r="T111" s="9"/>
-      <c r="U111" s="9"/>
+      <c r="Q111" s="36"/>
+      <c r="R111" s="28"/>
+      <c r="S111" s="36"/>
+      <c r="T111" s="36"/>
+      <c r="U111" s="36"/>
       <c r="V111" s="9"/>
       <c r="W111" s="9"/>
       <c r="X111" s="9"/>
@@ -18318,11 +18380,11 @@
       <c r="N112" s="9"/>
       <c r="O112" s="9"/>
       <c r="P112" s="9"/>
-      <c r="Q112" s="9"/>
-      <c r="R112" s="9"/>
-      <c r="S112" s="9"/>
-      <c r="T112" s="9"/>
-      <c r="U112" s="9"/>
+      <c r="Q112" s="36"/>
+      <c r="R112" s="28"/>
+      <c r="S112" s="36"/>
+      <c r="T112" s="36"/>
+      <c r="U112" s="36"/>
       <c r="V112" s="9"/>
       <c r="W112" s="9"/>
       <c r="X112" s="9"/>
@@ -18382,11 +18444,11 @@
       <c r="N113" s="9"/>
       <c r="O113" s="9"/>
       <c r="P113" s="9"/>
-      <c r="Q113" s="9"/>
-      <c r="R113" s="9"/>
-      <c r="S113" s="9"/>
-      <c r="T113" s="9"/>
-      <c r="U113" s="9"/>
+      <c r="Q113" s="36"/>
+      <c r="R113" s="28"/>
+      <c r="S113" s="36"/>
+      <c r="T113" s="36"/>
+      <c r="U113" s="36"/>
       <c r="V113" s="9"/>
       <c r="W113" s="9"/>
       <c r="X113" s="9"/>
@@ -18446,11 +18508,11 @@
       <c r="N114" s="9"/>
       <c r="O114" s="9"/>
       <c r="P114" s="9"/>
-      <c r="Q114" s="9"/>
-      <c r="R114" s="9"/>
-      <c r="S114" s="9"/>
-      <c r="T114" s="9"/>
-      <c r="U114" s="9"/>
+      <c r="Q114" s="36"/>
+      <c r="R114" s="28"/>
+      <c r="S114" s="36"/>
+      <c r="T114" s="36"/>
+      <c r="U114" s="36"/>
       <c r="V114" s="9"/>
       <c r="W114" s="9"/>
       <c r="X114" s="9"/>
@@ -18510,11 +18572,11 @@
       <c r="N115" s="9"/>
       <c r="O115" s="9"/>
       <c r="P115" s="9"/>
-      <c r="Q115" s="9"/>
-      <c r="R115" s="9"/>
-      <c r="S115" s="9"/>
-      <c r="T115" s="9"/>
-      <c r="U115" s="9"/>
+      <c r="Q115" s="36"/>
+      <c r="R115" s="28"/>
+      <c r="S115" s="36"/>
+      <c r="T115" s="36"/>
+      <c r="U115" s="36"/>
       <c r="V115" s="9"/>
       <c r="W115" s="9"/>
       <c r="X115" s="9"/>
@@ -18574,11 +18636,11 @@
       <c r="N116" s="9"/>
       <c r="O116" s="9"/>
       <c r="P116" s="9"/>
-      <c r="Q116" s="9"/>
-      <c r="R116" s="9"/>
-      <c r="S116" s="9"/>
-      <c r="T116" s="9"/>
-      <c r="U116" s="9"/>
+      <c r="Q116" s="36"/>
+      <c r="R116" s="28"/>
+      <c r="S116" s="36"/>
+      <c r="T116" s="36"/>
+      <c r="U116" s="36"/>
       <c r="V116" s="9"/>
       <c r="W116" s="9"/>
       <c r="X116" s="9"/>
@@ -18638,11 +18700,11 @@
       <c r="N117" s="9"/>
       <c r="O117" s="9"/>
       <c r="P117" s="9"/>
-      <c r="Q117" s="9"/>
-      <c r="R117" s="9"/>
-      <c r="S117" s="9"/>
-      <c r="T117" s="9"/>
-      <c r="U117" s="9"/>
+      <c r="Q117" s="36"/>
+      <c r="R117" s="28"/>
+      <c r="S117" s="36"/>
+      <c r="T117" s="36"/>
+      <c r="U117" s="36"/>
       <c r="V117" s="9"/>
       <c r="W117" s="9"/>
       <c r="X117" s="9"/>
@@ -18702,11 +18764,11 @@
       <c r="N118" s="9"/>
       <c r="O118" s="9"/>
       <c r="P118" s="9"/>
-      <c r="Q118" s="9"/>
-      <c r="R118" s="9"/>
-      <c r="S118" s="9"/>
-      <c r="T118" s="9"/>
-      <c r="U118" s="9"/>
+      <c r="Q118" s="36"/>
+      <c r="R118" s="28"/>
+      <c r="S118" s="36"/>
+      <c r="T118" s="36"/>
+      <c r="U118" s="36"/>
       <c r="V118" s="9"/>
       <c r="W118" s="9"/>
       <c r="X118" s="9"/>
@@ -18766,11 +18828,11 @@
       <c r="N119" s="9"/>
       <c r="O119" s="9"/>
       <c r="P119" s="9"/>
-      <c r="Q119" s="9"/>
-      <c r="R119" s="9"/>
-      <c r="S119" s="9"/>
-      <c r="T119" s="9"/>
-      <c r="U119" s="9"/>
+      <c r="Q119" s="36"/>
+      <c r="R119" s="28"/>
+      <c r="S119" s="36"/>
+      <c r="T119" s="36"/>
+      <c r="U119" s="36"/>
       <c r="V119" s="9"/>
       <c r="W119" s="9"/>
       <c r="X119" s="9"/>
@@ -18830,11 +18892,11 @@
       <c r="N120" s="9"/>
       <c r="O120" s="9"/>
       <c r="P120" s="9"/>
-      <c r="Q120" s="9"/>
-      <c r="R120" s="9"/>
-      <c r="S120" s="9"/>
-      <c r="T120" s="9"/>
-      <c r="U120" s="9"/>
+      <c r="Q120" s="36"/>
+      <c r="R120" s="28"/>
+      <c r="S120" s="36"/>
+      <c r="T120" s="36"/>
+      <c r="U120" s="36"/>
       <c r="V120" s="9"/>
       <c r="W120" s="9"/>
       <c r="X120" s="9"/>
@@ -18894,11 +18956,11 @@
       <c r="N121" s="9"/>
       <c r="O121" s="9"/>
       <c r="P121" s="9"/>
-      <c r="Q121" s="9"/>
-      <c r="R121" s="9"/>
-      <c r="S121" s="9"/>
-      <c r="T121" s="9"/>
-      <c r="U121" s="9"/>
+      <c r="Q121" s="36"/>
+      <c r="R121" s="28"/>
+      <c r="S121" s="36"/>
+      <c r="T121" s="36"/>
+      <c r="U121" s="36"/>
       <c r="V121" s="9"/>
       <c r="W121" s="9"/>
       <c r="X121" s="9"/>
@@ -18958,11 +19020,11 @@
       <c r="N122" s="9"/>
       <c r="O122" s="9"/>
       <c r="P122" s="9"/>
-      <c r="Q122" s="9"/>
-      <c r="R122" s="9"/>
-      <c r="S122" s="9"/>
-      <c r="T122" s="9"/>
-      <c r="U122" s="9"/>
+      <c r="Q122" s="36"/>
+      <c r="R122" s="28"/>
+      <c r="S122" s="36"/>
+      <c r="T122" s="36"/>
+      <c r="U122" s="36"/>
       <c r="V122" s="9"/>
       <c r="W122" s="9"/>
       <c r="X122" s="9"/>
@@ -19022,11 +19084,11 @@
       <c r="N123" s="9"/>
       <c r="O123" s="9"/>
       <c r="P123" s="9"/>
-      <c r="Q123" s="9"/>
-      <c r="R123" s="9"/>
-      <c r="S123" s="9"/>
-      <c r="T123" s="9"/>
-      <c r="U123" s="9"/>
+      <c r="Q123" s="36"/>
+      <c r="R123" s="28"/>
+      <c r="S123" s="36"/>
+      <c r="T123" s="36"/>
+      <c r="U123" s="36"/>
       <c r="V123" s="9"/>
       <c r="W123" s="9"/>
       <c r="X123" s="9"/>
@@ -19086,11 +19148,11 @@
       <c r="N124" s="9"/>
       <c r="O124" s="9"/>
       <c r="P124" s="9"/>
-      <c r="Q124" s="9"/>
-      <c r="R124" s="9"/>
-      <c r="S124" s="9"/>
-      <c r="T124" s="9"/>
-      <c r="U124" s="9"/>
+      <c r="Q124" s="36"/>
+      <c r="R124" s="28"/>
+      <c r="S124" s="36"/>
+      <c r="T124" s="36"/>
+      <c r="U124" s="36"/>
       <c r="V124" s="9"/>
       <c r="W124" s="9"/>
       <c r="X124" s="9"/>
@@ -19150,11 +19212,11 @@
       <c r="N125" s="9"/>
       <c r="O125" s="9"/>
       <c r="P125" s="9"/>
-      <c r="Q125" s="9"/>
-      <c r="R125" s="9"/>
-      <c r="S125" s="9"/>
-      <c r="T125" s="9"/>
-      <c r="U125" s="9"/>
+      <c r="Q125" s="36"/>
+      <c r="R125" s="28"/>
+      <c r="S125" s="36"/>
+      <c r="T125" s="36"/>
+      <c r="U125" s="36"/>
       <c r="V125" s="9"/>
       <c r="W125" s="9"/>
       <c r="X125" s="9"/>
@@ -19214,11 +19276,11 @@
       <c r="N126" s="9"/>
       <c r="O126" s="9"/>
       <c r="P126" s="9"/>
-      <c r="Q126" s="9"/>
-      <c r="R126" s="9"/>
-      <c r="S126" s="9"/>
-      <c r="T126" s="9"/>
-      <c r="U126" s="9"/>
+      <c r="Q126" s="36"/>
+      <c r="R126" s="28"/>
+      <c r="S126" s="36"/>
+      <c r="T126" s="36"/>
+      <c r="U126" s="36"/>
       <c r="V126" s="9"/>
       <c r="W126" s="9"/>
       <c r="X126" s="9"/>
@@ -19278,11 +19340,11 @@
       <c r="N127" s="9"/>
       <c r="O127" s="9"/>
       <c r="P127" s="9"/>
-      <c r="Q127" s="9"/>
-      <c r="R127" s="9"/>
-      <c r="S127" s="9"/>
-      <c r="T127" s="9"/>
-      <c r="U127" s="9"/>
+      <c r="Q127" s="36"/>
+      <c r="R127" s="28"/>
+      <c r="S127" s="36"/>
+      <c r="T127" s="36"/>
+      <c r="U127" s="36"/>
       <c r="V127" s="9"/>
       <c r="W127" s="9"/>
       <c r="X127" s="9"/>
@@ -19342,11 +19404,11 @@
       <c r="N128" s="9"/>
       <c r="O128" s="9"/>
       <c r="P128" s="9"/>
-      <c r="Q128" s="9"/>
-      <c r="R128" s="9"/>
-      <c r="S128" s="9"/>
-      <c r="T128" s="9"/>
-      <c r="U128" s="9"/>
+      <c r="Q128" s="36"/>
+      <c r="R128" s="28"/>
+      <c r="S128" s="36"/>
+      <c r="T128" s="36"/>
+      <c r="U128" s="36"/>
       <c r="V128" s="9"/>
       <c r="W128" s="9"/>
       <c r="X128" s="9"/>
@@ -19406,11 +19468,11 @@
       <c r="N129" s="9"/>
       <c r="O129" s="9"/>
       <c r="P129" s="9"/>
-      <c r="Q129" s="9"/>
-      <c r="R129" s="9"/>
-      <c r="S129" s="9"/>
-      <c r="T129" s="9"/>
-      <c r="U129" s="9"/>
+      <c r="Q129" s="36"/>
+      <c r="R129" s="28"/>
+      <c r="S129" s="36"/>
+      <c r="T129" s="36"/>
+      <c r="U129" s="36"/>
       <c r="V129" s="9"/>
       <c r="W129" s="9"/>
       <c r="X129" s="9"/>
@@ -19470,11 +19532,11 @@
       <c r="N130" s="9"/>
       <c r="O130" s="9"/>
       <c r="P130" s="9"/>
-      <c r="Q130" s="9"/>
-      <c r="R130" s="9"/>
-      <c r="S130" s="9"/>
-      <c r="T130" s="9"/>
-      <c r="U130" s="9"/>
+      <c r="Q130" s="36"/>
+      <c r="R130" s="28"/>
+      <c r="S130" s="36"/>
+      <c r="T130" s="36"/>
+      <c r="U130" s="36"/>
       <c r="V130" s="9"/>
       <c r="W130" s="9"/>
       <c r="X130" s="9"/>
@@ -19534,11 +19596,11 @@
       <c r="N131" s="9"/>
       <c r="O131" s="9"/>
       <c r="P131" s="9"/>
-      <c r="Q131" s="9"/>
-      <c r="R131" s="9"/>
-      <c r="S131" s="9"/>
-      <c r="T131" s="9"/>
-      <c r="U131" s="9"/>
+      <c r="Q131" s="36"/>
+      <c r="R131" s="28"/>
+      <c r="S131" s="36"/>
+      <c r="T131" s="36"/>
+      <c r="U131" s="36"/>
       <c r="V131" s="9"/>
       <c r="W131" s="9"/>
       <c r="X131" s="9"/>
@@ -19598,11 +19660,11 @@
       <c r="N132" s="9"/>
       <c r="O132" s="9"/>
       <c r="P132" s="9"/>
-      <c r="Q132" s="9"/>
-      <c r="R132" s="9"/>
-      <c r="S132" s="9"/>
-      <c r="T132" s="9"/>
-      <c r="U132" s="9"/>
+      <c r="Q132" s="36"/>
+      <c r="R132" s="28"/>
+      <c r="S132" s="36"/>
+      <c r="T132" s="36"/>
+      <c r="U132" s="36"/>
       <c r="V132" s="9"/>
       <c r="W132" s="9"/>
       <c r="X132" s="9"/>
@@ -19662,11 +19724,11 @@
       <c r="N133" s="9"/>
       <c r="O133" s="9"/>
       <c r="P133" s="9"/>
-      <c r="Q133" s="9"/>
-      <c r="R133" s="9"/>
-      <c r="S133" s="9"/>
-      <c r="T133" s="9"/>
-      <c r="U133" s="9"/>
+      <c r="Q133" s="36"/>
+      <c r="R133" s="28"/>
+      <c r="S133" s="36"/>
+      <c r="T133" s="36"/>
+      <c r="U133" s="36"/>
       <c r="V133" s="9"/>
       <c r="W133" s="9"/>
       <c r="X133" s="9"/>
@@ -19726,11 +19788,11 @@
       <c r="N134" s="9"/>
       <c r="O134" s="9"/>
       <c r="P134" s="9"/>
-      <c r="Q134" s="9"/>
-      <c r="R134" s="9"/>
-      <c r="S134" s="9"/>
-      <c r="T134" s="9"/>
-      <c r="U134" s="9"/>
+      <c r="Q134" s="36"/>
+      <c r="R134" s="28"/>
+      <c r="S134" s="36"/>
+      <c r="T134" s="36"/>
+      <c r="U134" s="36"/>
       <c r="V134" s="9"/>
       <c r="W134" s="9"/>
       <c r="X134" s="9"/>
@@ -19790,11 +19852,11 @@
       <c r="N135" s="9"/>
       <c r="O135" s="9"/>
       <c r="P135" s="9"/>
-      <c r="Q135" s="9"/>
-      <c r="R135" s="9"/>
-      <c r="S135" s="9"/>
-      <c r="T135" s="9"/>
-      <c r="U135" s="9"/>
+      <c r="Q135" s="36"/>
+      <c r="R135" s="28"/>
+      <c r="S135" s="36"/>
+      <c r="T135" s="36"/>
+      <c r="U135" s="36"/>
       <c r="V135" s="9"/>
       <c r="W135" s="9"/>
       <c r="X135" s="9"/>
@@ -19854,11 +19916,11 @@
       <c r="N136" s="9"/>
       <c r="O136" s="9"/>
       <c r="P136" s="9"/>
-      <c r="Q136" s="9"/>
-      <c r="R136" s="9"/>
-      <c r="S136" s="9"/>
-      <c r="T136" s="9"/>
-      <c r="U136" s="9"/>
+      <c r="Q136" s="36"/>
+      <c r="R136" s="28"/>
+      <c r="S136" s="36"/>
+      <c r="T136" s="36"/>
+      <c r="U136" s="36"/>
       <c r="V136" s="9"/>
       <c r="W136" s="9"/>
       <c r="X136" s="9"/>
@@ -19918,11 +19980,11 @@
       <c r="N137" s="9"/>
       <c r="O137" s="9"/>
       <c r="P137" s="9"/>
-      <c r="Q137" s="9"/>
-      <c r="R137" s="9"/>
-      <c r="S137" s="9"/>
-      <c r="T137" s="9"/>
-      <c r="U137" s="9"/>
+      <c r="Q137" s="36"/>
+      <c r="R137" s="28"/>
+      <c r="S137" s="36"/>
+      <c r="T137" s="36"/>
+      <c r="U137" s="36"/>
       <c r="V137" s="9"/>
       <c r="W137" s="9"/>
       <c r="X137" s="9"/>
@@ -19982,11 +20044,11 @@
       <c r="N138" s="9"/>
       <c r="O138" s="9"/>
       <c r="P138" s="9"/>
-      <c r="Q138" s="9"/>
-      <c r="R138" s="9"/>
-      <c r="S138" s="9"/>
-      <c r="T138" s="9"/>
-      <c r="U138" s="9"/>
+      <c r="Q138" s="36"/>
+      <c r="R138" s="28"/>
+      <c r="S138" s="36"/>
+      <c r="T138" s="36"/>
+      <c r="U138" s="36"/>
       <c r="V138" s="9"/>
       <c r="W138" s="9"/>
       <c r="X138" s="9"/>
@@ -20046,11 +20108,11 @@
       <c r="N139" s="9"/>
       <c r="O139" s="9"/>
       <c r="P139" s="9"/>
-      <c r="Q139" s="9"/>
-      <c r="R139" s="9"/>
-      <c r="S139" s="9"/>
-      <c r="T139" s="9"/>
-      <c r="U139" s="9"/>
+      <c r="Q139" s="36"/>
+      <c r="R139" s="28"/>
+      <c r="S139" s="36"/>
+      <c r="T139" s="36"/>
+      <c r="U139" s="36"/>
       <c r="V139" s="9"/>
       <c r="W139" s="9"/>
       <c r="X139" s="9"/>
@@ -20110,11 +20172,11 @@
       <c r="N140" s="9"/>
       <c r="O140" s="9"/>
       <c r="P140" s="9"/>
-      <c r="Q140" s="9"/>
-      <c r="R140" s="9"/>
-      <c r="S140" s="9"/>
-      <c r="T140" s="9"/>
-      <c r="U140" s="9"/>
+      <c r="Q140" s="36"/>
+      <c r="R140" s="28"/>
+      <c r="S140" s="36"/>
+      <c r="T140" s="36"/>
+      <c r="U140" s="36"/>
       <c r="V140" s="9"/>
       <c r="W140" s="9"/>
       <c r="X140" s="9"/>
@@ -20174,11 +20236,11 @@
       <c r="N141" s="9"/>
       <c r="O141" s="9"/>
       <c r="P141" s="9"/>
-      <c r="Q141" s="9"/>
-      <c r="R141" s="9"/>
-      <c r="S141" s="9"/>
-      <c r="T141" s="9"/>
-      <c r="U141" s="9"/>
+      <c r="Q141" s="36"/>
+      <c r="R141" s="28"/>
+      <c r="S141" s="36"/>
+      <c r="T141" s="36"/>
+      <c r="U141" s="36"/>
       <c r="V141" s="9"/>
       <c r="W141" s="9"/>
       <c r="X141" s="9"/>
@@ -20238,11 +20300,11 @@
       <c r="N142" s="9"/>
       <c r="O142" s="9"/>
       <c r="P142" s="9"/>
-      <c r="Q142" s="9"/>
-      <c r="R142" s="9"/>
-      <c r="S142" s="9"/>
-      <c r="T142" s="9"/>
-      <c r="U142" s="9"/>
+      <c r="Q142" s="36"/>
+      <c r="R142" s="28"/>
+      <c r="S142" s="36"/>
+      <c r="T142" s="36"/>
+      <c r="U142" s="36"/>
       <c r="V142" s="9"/>
       <c r="W142" s="9"/>
       <c r="X142" s="9"/>
@@ -20302,11 +20364,11 @@
       <c r="N143" s="9"/>
       <c r="O143" s="9"/>
       <c r="P143" s="9"/>
-      <c r="Q143" s="9"/>
-      <c r="R143" s="9"/>
-      <c r="S143" s="9"/>
-      <c r="T143" s="9"/>
-      <c r="U143" s="9"/>
+      <c r="Q143" s="36"/>
+      <c r="R143" s="28"/>
+      <c r="S143" s="36"/>
+      <c r="T143" s="36"/>
+      <c r="U143" s="36"/>
       <c r="V143" s="9"/>
       <c r="W143" s="9"/>
       <c r="X143" s="9"/>
@@ -20366,11 +20428,11 @@
       <c r="N144" s="9"/>
       <c r="O144" s="9"/>
       <c r="P144" s="9"/>
-      <c r="Q144" s="9"/>
-      <c r="R144" s="9"/>
-      <c r="S144" s="9"/>
-      <c r="T144" s="9"/>
-      <c r="U144" s="9"/>
+      <c r="Q144" s="36"/>
+      <c r="R144" s="28"/>
+      <c r="S144" s="36"/>
+      <c r="T144" s="36"/>
+      <c r="U144" s="36"/>
       <c r="V144" s="9"/>
       <c r="W144" s="9"/>
       <c r="X144" s="9"/>
@@ -20430,11 +20492,11 @@
       <c r="N145" s="9"/>
       <c r="O145" s="9"/>
       <c r="P145" s="9"/>
-      <c r="Q145" s="9"/>
-      <c r="R145" s="9"/>
-      <c r="S145" s="9"/>
-      <c r="T145" s="9"/>
-      <c r="U145" s="9"/>
+      <c r="Q145" s="36"/>
+      <c r="R145" s="28"/>
+      <c r="S145" s="36"/>
+      <c r="T145" s="36"/>
+      <c r="U145" s="36"/>
       <c r="V145" s="9"/>
       <c r="W145" s="9"/>
       <c r="X145" s="9"/>
@@ -20494,11 +20556,11 @@
       <c r="N146" s="9"/>
       <c r="O146" s="9"/>
       <c r="P146" s="9"/>
-      <c r="Q146" s="9"/>
-      <c r="R146" s="9"/>
-      <c r="S146" s="9"/>
-      <c r="T146" s="9"/>
-      <c r="U146" s="9"/>
+      <c r="Q146" s="36"/>
+      <c r="R146" s="28"/>
+      <c r="S146" s="36"/>
+      <c r="T146" s="36"/>
+      <c r="U146" s="36"/>
       <c r="V146" s="9"/>
       <c r="W146" s="9"/>
       <c r="X146" s="9"/>
@@ -20558,11 +20620,11 @@
       <c r="N147" s="9"/>
       <c r="O147" s="9"/>
       <c r="P147" s="9"/>
-      <c r="Q147" s="9"/>
-      <c r="R147" s="9"/>
-      <c r="S147" s="9"/>
-      <c r="T147" s="9"/>
-      <c r="U147" s="9"/>
+      <c r="Q147" s="36"/>
+      <c r="R147" s="28"/>
+      <c r="S147" s="36"/>
+      <c r="T147" s="36"/>
+      <c r="U147" s="36"/>
       <c r="V147" s="9"/>
       <c r="W147" s="9"/>
       <c r="X147" s="9"/>
@@ -20622,11 +20684,11 @@
       <c r="N148" s="9"/>
       <c r="O148" s="9"/>
       <c r="P148" s="9"/>
-      <c r="Q148" s="9"/>
-      <c r="R148" s="9"/>
-      <c r="S148" s="9"/>
-      <c r="T148" s="9"/>
-      <c r="U148" s="9"/>
+      <c r="Q148" s="36"/>
+      <c r="R148" s="28"/>
+      <c r="S148" s="36"/>
+      <c r="T148" s="36"/>
+      <c r="U148" s="36"/>
       <c r="V148" s="9"/>
       <c r="W148" s="9"/>
       <c r="X148" s="9"/>
@@ -20686,11 +20748,11 @@
       <c r="N149" s="9"/>
       <c r="O149" s="9"/>
       <c r="P149" s="9"/>
-      <c r="Q149" s="9"/>
-      <c r="R149" s="9"/>
-      <c r="S149" s="9"/>
-      <c r="T149" s="9"/>
-      <c r="U149" s="9"/>
+      <c r="Q149" s="36"/>
+      <c r="R149" s="28"/>
+      <c r="S149" s="36"/>
+      <c r="T149" s="36"/>
+      <c r="U149" s="36"/>
       <c r="V149" s="9"/>
       <c r="W149" s="9"/>
       <c r="X149" s="9"/>
@@ -20750,11 +20812,11 @@
       <c r="N150" s="9"/>
       <c r="O150" s="9"/>
       <c r="P150" s="9"/>
-      <c r="Q150" s="9"/>
-      <c r="R150" s="9"/>
-      <c r="S150" s="9"/>
-      <c r="T150" s="9"/>
-      <c r="U150" s="9"/>
+      <c r="Q150" s="36"/>
+      <c r="R150" s="28"/>
+      <c r="S150" s="36"/>
+      <c r="T150" s="36"/>
+      <c r="U150" s="36"/>
       <c r="V150" s="9"/>
       <c r="W150" s="9"/>
       <c r="X150" s="9"/>
@@ -20814,11 +20876,11 @@
       <c r="N151" s="9"/>
       <c r="O151" s="9"/>
       <c r="P151" s="9"/>
-      <c r="Q151" s="9"/>
-      <c r="R151" s="9"/>
-      <c r="S151" s="9"/>
-      <c r="T151" s="9"/>
-      <c r="U151" s="9"/>
+      <c r="Q151" s="36"/>
+      <c r="R151" s="28"/>
+      <c r="S151" s="36"/>
+      <c r="T151" s="36"/>
+      <c r="U151" s="36"/>
       <c r="V151" s="9"/>
       <c r="W151" s="9"/>
       <c r="X151" s="9"/>
@@ -20878,11 +20940,11 @@
       <c r="N152" s="9"/>
       <c r="O152" s="9"/>
       <c r="P152" s="9"/>
-      <c r="Q152" s="9"/>
-      <c r="R152" s="9"/>
-      <c r="S152" s="9"/>
-      <c r="T152" s="9"/>
-      <c r="U152" s="9"/>
+      <c r="Q152" s="36"/>
+      <c r="R152" s="28"/>
+      <c r="S152" s="36"/>
+      <c r="T152" s="36"/>
+      <c r="U152" s="36"/>
       <c r="V152" s="9"/>
       <c r="W152" s="9"/>
       <c r="X152" s="9"/>
@@ -20942,11 +21004,11 @@
       <c r="N153" s="9"/>
       <c r="O153" s="9"/>
       <c r="P153" s="9"/>
-      <c r="Q153" s="9"/>
-      <c r="R153" s="9"/>
-      <c r="S153" s="9"/>
-      <c r="T153" s="9"/>
-      <c r="U153" s="9"/>
+      <c r="Q153" s="36"/>
+      <c r="R153" s="28"/>
+      <c r="S153" s="36"/>
+      <c r="T153" s="36"/>
+      <c r="U153" s="36"/>
       <c r="V153" s="9"/>
       <c r="W153" s="9"/>
       <c r="X153" s="9"/>
@@ -21006,11 +21068,11 @@
       <c r="N154" s="9"/>
       <c r="O154" s="9"/>
       <c r="P154" s="9"/>
-      <c r="Q154" s="9"/>
-      <c r="R154" s="9"/>
-      <c r="S154" s="9"/>
-      <c r="T154" s="9"/>
-      <c r="U154" s="9"/>
+      <c r="Q154" s="36"/>
+      <c r="R154" s="28"/>
+      <c r="S154" s="36"/>
+      <c r="T154" s="36"/>
+      <c r="U154" s="36"/>
       <c r="V154" s="9"/>
       <c r="W154" s="9"/>
       <c r="X154" s="9"/>
@@ -21070,11 +21132,11 @@
       <c r="N155" s="9"/>
       <c r="O155" s="9"/>
       <c r="P155" s="9"/>
-      <c r="Q155" s="9"/>
-      <c r="R155" s="9"/>
-      <c r="S155" s="9"/>
-      <c r="T155" s="9"/>
-      <c r="U155" s="9"/>
+      <c r="Q155" s="36"/>
+      <c r="R155" s="28"/>
+      <c r="S155" s="36"/>
+      <c r="T155" s="36"/>
+      <c r="U155" s="36"/>
       <c r="V155" s="9"/>
       <c r="W155" s="9"/>
       <c r="X155" s="9"/>
@@ -21134,11 +21196,11 @@
       <c r="N156" s="9"/>
       <c r="O156" s="9"/>
       <c r="P156" s="9"/>
-      <c r="Q156" s="9"/>
-      <c r="R156" s="9"/>
-      <c r="S156" s="9"/>
-      <c r="T156" s="9"/>
-      <c r="U156" s="9"/>
+      <c r="Q156" s="36"/>
+      <c r="R156" s="28"/>
+      <c r="S156" s="36"/>
+      <c r="T156" s="36"/>
+      <c r="U156" s="36"/>
       <c r="V156" s="9"/>
       <c r="W156" s="9"/>
       <c r="X156" s="9"/>
@@ -21198,11 +21260,11 @@
       <c r="N157" s="9"/>
       <c r="O157" s="9"/>
       <c r="P157" s="9"/>
-      <c r="Q157" s="9"/>
-      <c r="R157" s="9"/>
-      <c r="S157" s="9"/>
-      <c r="T157" s="9"/>
-      <c r="U157" s="9"/>
+      <c r="Q157" s="36"/>
+      <c r="R157" s="28"/>
+      <c r="S157" s="36"/>
+      <c r="T157" s="36"/>
+      <c r="U157" s="36"/>
       <c r="V157" s="9"/>
       <c r="W157" s="9"/>
       <c r="X157" s="9"/>
@@ -21262,11 +21324,11 @@
       <c r="N158" s="9"/>
       <c r="O158" s="9"/>
       <c r="P158" s="9"/>
-      <c r="Q158" s="9"/>
-      <c r="R158" s="9"/>
-      <c r="S158" s="9"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
+      <c r="Q158" s="36"/>
+      <c r="R158" s="28"/>
+      <c r="S158" s="36"/>
+      <c r="T158" s="36"/>
+      <c r="U158" s="36"/>
       <c r="V158" s="9"/>
       <c r="W158" s="9"/>
       <c r="X158" s="9"/>
@@ -21326,11 +21388,11 @@
       <c r="N159" s="9"/>
       <c r="O159" s="9"/>
       <c r="P159" s="9"/>
-      <c r="Q159" s="9"/>
-      <c r="R159" s="9"/>
-      <c r="S159" s="9"/>
-      <c r="T159" s="9"/>
-      <c r="U159" s="9"/>
+      <c r="Q159" s="36"/>
+      <c r="R159" s="28"/>
+      <c r="S159" s="36"/>
+      <c r="T159" s="36"/>
+      <c r="U159" s="36"/>
       <c r="V159" s="9"/>
       <c r="W159" s="9"/>
       <c r="X159" s="9"/>
@@ -21390,11 +21452,11 @@
       <c r="N160" s="9"/>
       <c r="O160" s="9"/>
       <c r="P160" s="9"/>
-      <c r="Q160" s="9"/>
-      <c r="R160" s="9"/>
-      <c r="S160" s="9"/>
-      <c r="T160" s="9"/>
-      <c r="U160" s="9"/>
+      <c r="Q160" s="36"/>
+      <c r="R160" s="28"/>
+      <c r="S160" s="36"/>
+      <c r="T160" s="36"/>
+      <c r="U160" s="36"/>
       <c r="V160" s="9"/>
       <c r="W160" s="9"/>
       <c r="X160" s="9"/>
@@ -21454,11 +21516,11 @@
       <c r="N161" s="9"/>
       <c r="O161" s="9"/>
       <c r="P161" s="9"/>
-      <c r="Q161" s="9"/>
-      <c r="R161" s="9"/>
-      <c r="S161" s="9"/>
-      <c r="T161" s="9"/>
-      <c r="U161" s="9"/>
+      <c r="Q161" s="36"/>
+      <c r="R161" s="28"/>
+      <c r="S161" s="36"/>
+      <c r="T161" s="36"/>
+      <c r="U161" s="36"/>
       <c r="V161" s="9"/>
       <c r="W161" s="9"/>
       <c r="X161" s="9"/>
@@ -21518,11 +21580,11 @@
       <c r="N162" s="9"/>
       <c r="O162" s="9"/>
       <c r="P162" s="9"/>
-      <c r="Q162" s="9"/>
-      <c r="R162" s="9"/>
-      <c r="S162" s="9"/>
-      <c r="T162" s="9"/>
-      <c r="U162" s="9"/>
+      <c r="Q162" s="36"/>
+      <c r="R162" s="28"/>
+      <c r="S162" s="36"/>
+      <c r="T162" s="36"/>
+      <c r="U162" s="36"/>
       <c r="V162" s="9"/>
       <c r="W162" s="9"/>
       <c r="X162" s="9"/>
@@ -21582,11 +21644,11 @@
       <c r="N163" s="9"/>
       <c r="O163" s="9"/>
       <c r="P163" s="9"/>
-      <c r="Q163" s="9"/>
-      <c r="R163" s="9"/>
-      <c r="S163" s="9"/>
-      <c r="T163" s="9"/>
-      <c r="U163" s="9"/>
+      <c r="Q163" s="36"/>
+      <c r="R163" s="28"/>
+      <c r="S163" s="36"/>
+      <c r="T163" s="36"/>
+      <c r="U163" s="36"/>
       <c r="V163" s="9"/>
       <c r="W163" s="9"/>
       <c r="X163" s="9"/>
@@ -21646,11 +21708,11 @@
       <c r="N164" s="9"/>
       <c r="O164" s="9"/>
       <c r="P164" s="9"/>
-      <c r="Q164" s="9"/>
-      <c r="R164" s="9"/>
-      <c r="S164" s="9"/>
-      <c r="T164" s="9"/>
-      <c r="U164" s="9"/>
+      <c r="Q164" s="36"/>
+      <c r="R164" s="28"/>
+      <c r="S164" s="36"/>
+      <c r="T164" s="36"/>
+      <c r="U164" s="36"/>
       <c r="V164" s="9"/>
       <c r="W164" s="9"/>
       <c r="X164" s="9"/>
@@ -21710,11 +21772,11 @@
       <c r="N165" s="9"/>
       <c r="O165" s="9"/>
       <c r="P165" s="9"/>
-      <c r="Q165" s="9"/>
-      <c r="R165" s="9"/>
-      <c r="S165" s="9"/>
-      <c r="T165" s="9"/>
-      <c r="U165" s="9"/>
+      <c r="Q165" s="36"/>
+      <c r="R165" s="28"/>
+      <c r="S165" s="36"/>
+      <c r="T165" s="36"/>
+      <c r="U165" s="36"/>
       <c r="V165" s="9"/>
       <c r="W165" s="9"/>
       <c r="X165" s="9"/>
@@ -21774,11 +21836,11 @@
       <c r="N166" s="9"/>
       <c r="O166" s="9"/>
       <c r="P166" s="9"/>
-      <c r="Q166" s="9"/>
-      <c r="R166" s="9"/>
-      <c r="S166" s="9"/>
-      <c r="T166" s="9"/>
-      <c r="U166" s="9"/>
+      <c r="Q166" s="36"/>
+      <c r="R166" s="28"/>
+      <c r="S166" s="36"/>
+      <c r="T166" s="36"/>
+      <c r="U166" s="36"/>
       <c r="V166" s="9"/>
       <c r="W166" s="9"/>
       <c r="X166" s="9"/>
@@ -21838,11 +21900,11 @@
       <c r="N167" s="9"/>
       <c r="O167" s="9"/>
       <c r="P167" s="9"/>
-      <c r="Q167" s="9"/>
-      <c r="R167" s="9"/>
-      <c r="S167" s="9"/>
-      <c r="T167" s="9"/>
-      <c r="U167" s="9"/>
+      <c r="Q167" s="36"/>
+      <c r="R167" s="28"/>
+      <c r="S167" s="36"/>
+      <c r="T167" s="36"/>
+      <c r="U167" s="36"/>
       <c r="V167" s="9"/>
       <c r="W167" s="9"/>
       <c r="X167" s="9"/>
@@ -21902,11 +21964,11 @@
       <c r="N168" s="9"/>
       <c r="O168" s="9"/>
       <c r="P168" s="9"/>
-      <c r="Q168" s="9"/>
-      <c r="R168" s="9"/>
-      <c r="S168" s="9"/>
-      <c r="T168" s="9"/>
-      <c r="U168" s="9"/>
+      <c r="Q168" s="36"/>
+      <c r="R168" s="28"/>
+      <c r="S168" s="36"/>
+      <c r="T168" s="36"/>
+      <c r="U168" s="36"/>
       <c r="V168" s="9"/>
       <c r="W168" s="9"/>
       <c r="X168" s="9"/>
@@ -21966,11 +22028,11 @@
       <c r="N169" s="9"/>
       <c r="O169" s="9"/>
       <c r="P169" s="9"/>
-      <c r="Q169" s="9"/>
-      <c r="R169" s="9"/>
-      <c r="S169" s="9"/>
-      <c r="T169" s="9"/>
-      <c r="U169" s="9"/>
+      <c r="Q169" s="36"/>
+      <c r="R169" s="28"/>
+      <c r="S169" s="36"/>
+      <c r="T169" s="36"/>
+      <c r="U169" s="36"/>
       <c r="V169" s="9"/>
       <c r="W169" s="9"/>
       <c r="X169" s="9"/>
@@ -22030,11 +22092,11 @@
       <c r="N170" s="9"/>
       <c r="O170" s="9"/>
       <c r="P170" s="9"/>
-      <c r="Q170" s="9"/>
-      <c r="R170" s="9"/>
-      <c r="S170" s="9"/>
-      <c r="T170" s="9"/>
-      <c r="U170" s="9"/>
+      <c r="Q170" s="36"/>
+      <c r="R170" s="28"/>
+      <c r="S170" s="36"/>
+      <c r="T170" s="36"/>
+      <c r="U170" s="36"/>
       <c r="V170" s="9"/>
       <c r="W170" s="9"/>
       <c r="X170" s="9"/>
@@ -22094,11 +22156,11 @@
       <c r="N171" s="9"/>
       <c r="O171" s="9"/>
       <c r="P171" s="9"/>
-      <c r="Q171" s="9"/>
-      <c r="R171" s="9"/>
-      <c r="S171" s="9"/>
-      <c r="T171" s="9"/>
-      <c r="U171" s="9"/>
+      <c r="Q171" s="36"/>
+      <c r="R171" s="28"/>
+      <c r="S171" s="36"/>
+      <c r="T171" s="36"/>
+      <c r="U171" s="36"/>
       <c r="V171" s="9"/>
       <c r="W171" s="9"/>
       <c r="X171" s="9"/>
@@ -22158,11 +22220,11 @@
       <c r="N172" s="9"/>
       <c r="O172" s="9"/>
       <c r="P172" s="9"/>
-      <c r="Q172" s="9"/>
-      <c r="R172" s="9"/>
-      <c r="S172" s="9"/>
-      <c r="T172" s="9"/>
-      <c r="U172" s="9"/>
+      <c r="Q172" s="36"/>
+      <c r="R172" s="28"/>
+      <c r="S172" s="36"/>
+      <c r="T172" s="36"/>
+      <c r="U172" s="36"/>
       <c r="V172" s="9"/>
       <c r="W172" s="9"/>
       <c r="X172" s="9"/>
@@ -22222,11 +22284,11 @@
       <c r="N173" s="9"/>
       <c r="O173" s="9"/>
       <c r="P173" s="9"/>
-      <c r="Q173" s="9"/>
-      <c r="R173" s="9"/>
-      <c r="S173" s="9"/>
-      <c r="T173" s="9"/>
-      <c r="U173" s="9"/>
+      <c r="Q173" s="36"/>
+      <c r="R173" s="28"/>
+      <c r="S173" s="36"/>
+      <c r="T173" s="36"/>
+      <c r="U173" s="36"/>
       <c r="V173" s="9"/>
       <c r="W173" s="9"/>
       <c r="X173" s="9"/>
@@ -22286,11 +22348,11 @@
       <c r="N174" s="9"/>
       <c r="O174" s="9"/>
       <c r="P174" s="9"/>
-      <c r="Q174" s="9"/>
-      <c r="R174" s="9"/>
-      <c r="S174" s="9"/>
-      <c r="T174" s="9"/>
-      <c r="U174" s="9"/>
+      <c r="Q174" s="36"/>
+      <c r="R174" s="28"/>
+      <c r="S174" s="36"/>
+      <c r="T174" s="36"/>
+      <c r="U174" s="36"/>
       <c r="V174" s="9"/>
       <c r="W174" s="9"/>
       <c r="X174" s="9"/>
@@ -22350,11 +22412,11 @@
       <c r="N175" s="9"/>
       <c r="O175" s="9"/>
       <c r="P175" s="9"/>
-      <c r="Q175" s="9"/>
-      <c r="R175" s="9"/>
-      <c r="S175" s="9"/>
-      <c r="T175" s="9"/>
-      <c r="U175" s="9"/>
+      <c r="Q175" s="36"/>
+      <c r="R175" s="28"/>
+      <c r="S175" s="36"/>
+      <c r="T175" s="36"/>
+      <c r="U175" s="36"/>
       <c r="V175" s="9"/>
       <c r="W175" s="9"/>
       <c r="X175" s="9"/>
@@ -22414,11 +22476,11 @@
       <c r="N176" s="9"/>
       <c r="O176" s="9"/>
       <c r="P176" s="9"/>
-      <c r="Q176" s="9"/>
-      <c r="R176" s="9"/>
-      <c r="S176" s="9"/>
-      <c r="T176" s="9"/>
-      <c r="U176" s="9"/>
+      <c r="Q176" s="36"/>
+      <c r="R176" s="28"/>
+      <c r="S176" s="36"/>
+      <c r="T176" s="36"/>
+      <c r="U176" s="36"/>
       <c r="V176" s="9"/>
       <c r="W176" s="9"/>
       <c r="X176" s="9"/>
@@ -22478,11 +22540,11 @@
       <c r="N177" s="9"/>
       <c r="O177" s="9"/>
       <c r="P177" s="9"/>
-      <c r="Q177" s="9"/>
-      <c r="R177" s="9"/>
-      <c r="S177" s="9"/>
-      <c r="T177" s="9"/>
-      <c r="U177" s="9"/>
+      <c r="Q177" s="36"/>
+      <c r="R177" s="28"/>
+      <c r="S177" s="36"/>
+      <c r="T177" s="36"/>
+      <c r="U177" s="36"/>
       <c r="V177" s="9"/>
       <c r="W177" s="9"/>
       <c r="X177" s="9"/>
@@ -22542,11 +22604,11 @@
       <c r="N178" s="9"/>
       <c r="O178" s="9"/>
       <c r="P178" s="9"/>
-      <c r="Q178" s="9"/>
-      <c r="R178" s="9"/>
-      <c r="S178" s="9"/>
-      <c r="T178" s="9"/>
-      <c r="U178" s="9"/>
+      <c r="Q178" s="36"/>
+      <c r="R178" s="28"/>
+      <c r="S178" s="36"/>
+      <c r="T178" s="36"/>
+      <c r="U178" s="36"/>
       <c r="V178" s="9"/>
       <c r="W178" s="9"/>
       <c r="X178" s="9"/>
@@ -22606,11 +22668,11 @@
       <c r="N179" s="9"/>
       <c r="O179" s="9"/>
       <c r="P179" s="9"/>
-      <c r="Q179" s="9"/>
-      <c r="R179" s="9"/>
-      <c r="S179" s="9"/>
-      <c r="T179" s="9"/>
-      <c r="U179" s="9"/>
+      <c r="Q179" s="36"/>
+      <c r="R179" s="28"/>
+      <c r="S179" s="36"/>
+      <c r="T179" s="36"/>
+      <c r="U179" s="36"/>
       <c r="V179" s="9"/>
       <c r="W179" s="9"/>
       <c r="X179" s="9"/>
@@ -22670,11 +22732,11 @@
       <c r="N180" s="9"/>
       <c r="O180" s="9"/>
       <c r="P180" s="9"/>
-      <c r="Q180" s="9"/>
-      <c r="R180" s="9"/>
-      <c r="S180" s="9"/>
-      <c r="T180" s="9"/>
-      <c r="U180" s="9"/>
+      <c r="Q180" s="36"/>
+      <c r="R180" s="28"/>
+      <c r="S180" s="36"/>
+      <c r="T180" s="36"/>
+      <c r="U180" s="36"/>
       <c r="V180" s="9"/>
       <c r="W180" s="9"/>
       <c r="X180" s="9"/>
@@ -22734,11 +22796,11 @@
       <c r="N181" s="9"/>
       <c r="O181" s="9"/>
       <c r="P181" s="9"/>
-      <c r="Q181" s="9"/>
-      <c r="R181" s="9"/>
-      <c r="S181" s="9"/>
-      <c r="T181" s="9"/>
-      <c r="U181" s="9"/>
+      <c r="Q181" s="36"/>
+      <c r="R181" s="28"/>
+      <c r="S181" s="36"/>
+      <c r="T181" s="36"/>
+      <c r="U181" s="36"/>
       <c r="V181" s="9"/>
       <c r="W181" s="9"/>
       <c r="X181" s="9"/>
@@ -22798,11 +22860,11 @@
       <c r="N182" s="9"/>
       <c r="O182" s="9"/>
       <c r="P182" s="9"/>
-      <c r="Q182" s="9"/>
-      <c r="R182" s="9"/>
-      <c r="S182" s="9"/>
-      <c r="T182" s="9"/>
-      <c r="U182" s="9"/>
+      <c r="Q182" s="36"/>
+      <c r="R182" s="28"/>
+      <c r="S182" s="36"/>
+      <c r="T182" s="36"/>
+      <c r="U182" s="36"/>
       <c r="V182" s="9"/>
       <c r="W182" s="9"/>
       <c r="X182" s="9"/>
@@ -22862,11 +22924,11 @@
       <c r="N183" s="9"/>
       <c r="O183" s="9"/>
       <c r="P183" s="9"/>
-      <c r="Q183" s="9"/>
-      <c r="R183" s="9"/>
-      <c r="S183" s="9"/>
-      <c r="T183" s="9"/>
-      <c r="U183" s="9"/>
+      <c r="Q183" s="36"/>
+      <c r="R183" s="28"/>
+      <c r="S183" s="36"/>
+      <c r="T183" s="36"/>
+      <c r="U183" s="36"/>
       <c r="V183" s="9"/>
       <c r="W183" s="9"/>
       <c r="X183" s="9"/>
@@ -22926,11 +22988,11 @@
       <c r="N184" s="9"/>
       <c r="O184" s="9"/>
       <c r="P184" s="9"/>
-      <c r="Q184" s="9"/>
-      <c r="R184" s="9"/>
-      <c r="S184" s="9"/>
-      <c r="T184" s="9"/>
-      <c r="U184" s="9"/>
+      <c r="Q184" s="36"/>
+      <c r="R184" s="28"/>
+      <c r="S184" s="36"/>
+      <c r="T184" s="36"/>
+      <c r="U184" s="36"/>
       <c r="V184" s="9"/>
       <c r="W184" s="9"/>
       <c r="X184" s="9"/>
@@ -22990,11 +23052,11 @@
       <c r="N185" s="9"/>
       <c r="O185" s="9"/>
       <c r="P185" s="9"/>
-      <c r="Q185" s="9"/>
-      <c r="R185" s="9"/>
-      <c r="S185" s="9"/>
-      <c r="T185" s="9"/>
-      <c r="U185" s="9"/>
+      <c r="Q185" s="36"/>
+      <c r="R185" s="28"/>
+      <c r="S185" s="36"/>
+      <c r="T185" s="36"/>
+      <c r="U185" s="36"/>
       <c r="V185" s="9"/>
       <c r="W185" s="9"/>
       <c r="X185" s="9"/>
@@ -23054,11 +23116,11 @@
       <c r="N186" s="9"/>
       <c r="O186" s="9"/>
       <c r="P186" s="9"/>
-      <c r="Q186" s="9"/>
-      <c r="R186" s="9"/>
-      <c r="S186" s="9"/>
-      <c r="T186" s="9"/>
-      <c r="U186" s="9"/>
+      <c r="Q186" s="36"/>
+      <c r="R186" s="28"/>
+      <c r="S186" s="36"/>
+      <c r="T186" s="36"/>
+      <c r="U186" s="36"/>
       <c r="V186" s="9"/>
       <c r="W186" s="9"/>
       <c r="X186" s="9"/>
@@ -23118,11 +23180,11 @@
       <c r="N187" s="9"/>
       <c r="O187" s="9"/>
       <c r="P187" s="9"/>
-      <c r="Q187" s="9"/>
-      <c r="R187" s="9"/>
-      <c r="S187" s="9"/>
-      <c r="T187" s="9"/>
-      <c r="U187" s="9"/>
+      <c r="Q187" s="36"/>
+      <c r="R187" s="28"/>
+      <c r="S187" s="36"/>
+      <c r="T187" s="36"/>
+      <c r="U187" s="36"/>
       <c r="V187" s="9"/>
       <c r="W187" s="9"/>
       <c r="X187" s="9"/>
@@ -23182,11 +23244,11 @@
       <c r="N188" s="9"/>
       <c r="O188" s="9"/>
       <c r="P188" s="9"/>
-      <c r="Q188" s="9"/>
-      <c r="R188" s="9"/>
-      <c r="S188" s="9"/>
-      <c r="T188" s="9"/>
-      <c r="U188" s="9"/>
+      <c r="Q188" s="36"/>
+      <c r="R188" s="28"/>
+      <c r="S188" s="36"/>
+      <c r="T188" s="36"/>
+      <c r="U188" s="36"/>
       <c r="V188" s="9"/>
       <c r="W188" s="9"/>
       <c r="X188" s="9"/>
@@ -23246,11 +23308,11 @@
       <c r="N189" s="9"/>
       <c r="O189" s="9"/>
       <c r="P189" s="9"/>
-      <c r="Q189" s="9"/>
-      <c r="R189" s="9"/>
-      <c r="S189" s="9"/>
-      <c r="T189" s="9"/>
-      <c r="U189" s="9"/>
+      <c r="Q189" s="36"/>
+      <c r="R189" s="28"/>
+      <c r="S189" s="36"/>
+      <c r="T189" s="36"/>
+      <c r="U189" s="36"/>
       <c r="V189" s="9"/>
       <c r="W189" s="9"/>
       <c r="X189" s="9"/>
@@ -23310,11 +23372,11 @@
       <c r="N190" s="9"/>
       <c r="O190" s="9"/>
       <c r="P190" s="9"/>
-      <c r="Q190" s="9"/>
-      <c r="R190" s="9"/>
-      <c r="S190" s="9"/>
-      <c r="T190" s="9"/>
-      <c r="U190" s="9"/>
+      <c r="Q190" s="36"/>
+      <c r="R190" s="28"/>
+      <c r="S190" s="36"/>
+      <c r="T190" s="36"/>
+      <c r="U190" s="36"/>
       <c r="V190" s="9"/>
       <c r="W190" s="9"/>
       <c r="X190" s="9"/>
@@ -23374,11 +23436,11 @@
       <c r="N191" s="9"/>
       <c r="O191" s="9"/>
       <c r="P191" s="9"/>
-      <c r="Q191" s="9"/>
-      <c r="R191" s="9"/>
-      <c r="S191" s="9"/>
-      <c r="T191" s="9"/>
-      <c r="U191" s="9"/>
+      <c r="Q191" s="36"/>
+      <c r="R191" s="28"/>
+      <c r="S191" s="36"/>
+      <c r="T191" s="36"/>
+      <c r="U191" s="36"/>
       <c r="V191" s="9"/>
       <c r="W191" s="9"/>
       <c r="X191" s="9"/>
@@ -23438,11 +23500,11 @@
       <c r="N192" s="9"/>
       <c r="O192" s="9"/>
       <c r="P192" s="9"/>
-      <c r="Q192" s="9"/>
-      <c r="R192" s="9"/>
-      <c r="S192" s="9"/>
-      <c r="T192" s="9"/>
-      <c r="U192" s="9"/>
+      <c r="Q192" s="36"/>
+      <c r="R192" s="28"/>
+      <c r="S192" s="36"/>
+      <c r="T192" s="36"/>
+      <c r="U192" s="36"/>
       <c r="V192" s="9"/>
       <c r="W192" s="9"/>
       <c r="X192" s="9"/>
@@ -23502,11 +23564,11 @@
       <c r="N193" s="9"/>
       <c r="O193" s="9"/>
       <c r="P193" s="9"/>
-      <c r="Q193" s="9"/>
-      <c r="R193" s="9"/>
-      <c r="S193" s="9"/>
-      <c r="T193" s="9"/>
-      <c r="U193" s="9"/>
+      <c r="Q193" s="36"/>
+      <c r="R193" s="28"/>
+      <c r="S193" s="36"/>
+      <c r="T193" s="36"/>
+      <c r="U193" s="36"/>
       <c r="V193" s="9"/>
       <c r="W193" s="9"/>
       <c r="X193" s="9"/>
@@ -23566,11 +23628,11 @@
       <c r="N194" s="9"/>
       <c r="O194" s="9"/>
       <c r="P194" s="9"/>
-      <c r="Q194" s="9"/>
-      <c r="R194" s="9"/>
-      <c r="S194" s="9"/>
-      <c r="T194" s="9"/>
-      <c r="U194" s="9"/>
+      <c r="Q194" s="36"/>
+      <c r="R194" s="28"/>
+      <c r="S194" s="36"/>
+      <c r="T194" s="36"/>
+      <c r="U194" s="36"/>
       <c r="V194" s="9"/>
       <c r="W194" s="9"/>
       <c r="X194" s="9"/>
@@ -23630,11 +23692,11 @@
       <c r="N195" s="9"/>
       <c r="O195" s="9"/>
       <c r="P195" s="9"/>
-      <c r="Q195" s="9"/>
-      <c r="R195" s="9"/>
-      <c r="S195" s="9"/>
-      <c r="T195" s="9"/>
-      <c r="U195" s="9"/>
+      <c r="Q195" s="36"/>
+      <c r="R195" s="28"/>
+      <c r="S195" s="36"/>
+      <c r="T195" s="36"/>
+      <c r="U195" s="36"/>
       <c r="V195" s="9"/>
       <c r="W195" s="9"/>
       <c r="X195" s="9"/>
@@ -23694,11 +23756,11 @@
       <c r="N196" s="9"/>
       <c r="O196" s="9"/>
       <c r="P196" s="9"/>
-      <c r="Q196" s="9"/>
-      <c r="R196" s="9"/>
-      <c r="S196" s="9"/>
-      <c r="T196" s="9"/>
-      <c r="U196" s="9"/>
+      <c r="Q196" s="36"/>
+      <c r="R196" s="28"/>
+      <c r="S196" s="36"/>
+      <c r="T196" s="36"/>
+      <c r="U196" s="36"/>
       <c r="V196" s="9"/>
       <c r="W196" s="9"/>
       <c r="X196" s="9"/>
@@ -23758,11 +23820,11 @@
       <c r="N197" s="9"/>
       <c r="O197" s="9"/>
       <c r="P197" s="9"/>
-      <c r="Q197" s="9"/>
-      <c r="R197" s="9"/>
-      <c r="S197" s="9"/>
-      <c r="T197" s="9"/>
-      <c r="U197" s="9"/>
+      <c r="Q197" s="36"/>
+      <c r="R197" s="28"/>
+      <c r="S197" s="36"/>
+      <c r="T197" s="36"/>
+      <c r="U197" s="36"/>
       <c r="V197" s="9"/>
       <c r="W197" s="9"/>
       <c r="X197" s="9"/>
@@ -23822,11 +23884,11 @@
       <c r="N198" s="9"/>
       <c r="O198" s="9"/>
       <c r="P198" s="9"/>
-      <c r="Q198" s="9"/>
-      <c r="R198" s="9"/>
-      <c r="S198" s="9"/>
-      <c r="T198" s="9"/>
-      <c r="U198" s="9"/>
+      <c r="Q198" s="36"/>
+      <c r="R198" s="28"/>
+      <c r="S198" s="36"/>
+      <c r="T198" s="36"/>
+      <c r="U198" s="36"/>
       <c r="V198" s="9"/>
       <c r="W198" s="9"/>
       <c r="X198" s="9"/>
@@ -23886,11 +23948,11 @@
       <c r="N199" s="9"/>
       <c r="O199" s="9"/>
       <c r="P199" s="9"/>
-      <c r="Q199" s="9"/>
-      <c r="R199" s="9"/>
-      <c r="S199" s="9"/>
-      <c r="T199" s="9"/>
-      <c r="U199" s="9"/>
+      <c r="Q199" s="36"/>
+      <c r="R199" s="28"/>
+      <c r="S199" s="36"/>
+      <c r="T199" s="36"/>
+      <c r="U199" s="36"/>
       <c r="V199" s="9"/>
       <c r="W199" s="9"/>
       <c r="X199" s="9"/>
@@ -23950,11 +24012,11 @@
       <c r="N200" s="9"/>
       <c r="O200" s="9"/>
       <c r="P200" s="9"/>
-      <c r="Q200" s="9"/>
-      <c r="R200" s="9"/>
-      <c r="S200" s="9"/>
-      <c r="T200" s="9"/>
-      <c r="U200" s="9"/>
+      <c r="Q200" s="36"/>
+      <c r="R200" s="28"/>
+      <c r="S200" s="36"/>
+      <c r="T200" s="36"/>
+      <c r="U200" s="36"/>
       <c r="V200" s="9"/>
       <c r="W200" s="9"/>
       <c r="X200" s="9"/>
@@ -24014,11 +24076,11 @@
       <c r="N201" s="9"/>
       <c r="O201" s="9"/>
       <c r="P201" s="9"/>
-      <c r="Q201" s="9"/>
-      <c r="R201" s="9"/>
-      <c r="S201" s="9"/>
-      <c r="T201" s="9"/>
-      <c r="U201" s="9"/>
+      <c r="Q201" s="36"/>
+      <c r="R201" s="28"/>
+      <c r="S201" s="36"/>
+      <c r="T201" s="36"/>
+      <c r="U201" s="36"/>
       <c r="V201" s="9"/>
       <c r="W201" s="9"/>
       <c r="X201" s="9"/>
@@ -24078,11 +24140,11 @@
       <c r="N202" s="9"/>
       <c r="O202" s="9"/>
       <c r="P202" s="9"/>
-      <c r="Q202" s="9"/>
-      <c r="R202" s="9"/>
-      <c r="S202" s="9"/>
-      <c r="T202" s="9"/>
-      <c r="U202" s="9"/>
+      <c r="Q202" s="36"/>
+      <c r="R202" s="28"/>
+      <c r="S202" s="36"/>
+      <c r="T202" s="36"/>
+      <c r="U202" s="36"/>
       <c r="V202" s="9"/>
       <c r="W202" s="9"/>
       <c r="X202" s="9"/>
@@ -24142,11 +24204,11 @@
       <c r="N203" s="9"/>
       <c r="O203" s="9"/>
       <c r="P203" s="9"/>
-      <c r="Q203" s="9"/>
-      <c r="R203" s="9"/>
-      <c r="S203" s="9"/>
-      <c r="T203" s="9"/>
-      <c r="U203" s="9"/>
+      <c r="Q203" s="36"/>
+      <c r="R203" s="28"/>
+      <c r="S203" s="36"/>
+      <c r="T203" s="36"/>
+      <c r="U203" s="36"/>
       <c r="V203" s="9"/>
       <c r="W203" s="9"/>
       <c r="X203" s="9"/>
@@ -24206,11 +24268,11 @@
       <c r="N204" s="9"/>
       <c r="O204" s="9"/>
       <c r="P204" s="9"/>
-      <c r="Q204" s="9"/>
-      <c r="R204" s="9"/>
-      <c r="S204" s="9"/>
-      <c r="T204" s="9"/>
-      <c r="U204" s="9"/>
+      <c r="Q204" s="36"/>
+      <c r="R204" s="28"/>
+      <c r="S204" s="36"/>
+      <c r="T204" s="36"/>
+      <c r="U204" s="36"/>
       <c r="V204" s="9"/>
       <c r="W204" s="9"/>
       <c r="X204" s="9"/>
@@ -24270,11 +24332,11 @@
       <c r="N205" s="9"/>
       <c r="O205" s="9"/>
       <c r="P205" s="9"/>
-      <c r="Q205" s="9"/>
-      <c r="R205" s="9"/>
-      <c r="S205" s="9"/>
-      <c r="T205" s="9"/>
-      <c r="U205" s="9"/>
+      <c r="Q205" s="36"/>
+      <c r="R205" s="28"/>
+      <c r="S205" s="36"/>
+      <c r="T205" s="36"/>
+      <c r="U205" s="36"/>
       <c r="V205" s="9"/>
       <c r="W205" s="9"/>
       <c r="X205" s="9"/>
@@ -24334,11 +24396,11 @@
       <c r="N206" s="9"/>
       <c r="O206" s="9"/>
       <c r="P206" s="9"/>
-      <c r="Q206" s="9"/>
-      <c r="R206" s="9"/>
-      <c r="S206" s="9"/>
-      <c r="T206" s="9"/>
-      <c r="U206" s="9"/>
+      <c r="Q206" s="36"/>
+      <c r="R206" s="28"/>
+      <c r="S206" s="36"/>
+      <c r="T206" s="36"/>
+      <c r="U206" s="36"/>
       <c r="V206" s="9"/>
       <c r="W206" s="9"/>
       <c r="X206" s="9"/>
@@ -24398,11 +24460,11 @@
       <c r="N207" s="9"/>
       <c r="O207" s="9"/>
       <c r="P207" s="9"/>
-      <c r="Q207" s="9"/>
-      <c r="R207" s="9"/>
-      <c r="S207" s="9"/>
-      <c r="T207" s="9"/>
-      <c r="U207" s="9"/>
+      <c r="Q207" s="36"/>
+      <c r="R207" s="28"/>
+      <c r="S207" s="36"/>
+      <c r="T207" s="36"/>
+      <c r="U207" s="36"/>
       <c r="V207" s="9"/>
       <c r="W207" s="9"/>
       <c r="X207" s="9"/>
@@ -24462,11 +24524,11 @@
       <c r="N208" s="9"/>
       <c r="O208" s="9"/>
       <c r="P208" s="9"/>
-      <c r="Q208" s="9"/>
-      <c r="R208" s="9"/>
-      <c r="S208" s="9"/>
-      <c r="T208" s="9"/>
-      <c r="U208" s="9"/>
+      <c r="Q208" s="36"/>
+      <c r="R208" s="28"/>
+      <c r="S208" s="36"/>
+      <c r="T208" s="36"/>
+      <c r="U208" s="36"/>
       <c r="V208" s="9"/>
       <c r="W208" s="9"/>
       <c r="X208" s="9"/>
@@ -24526,11 +24588,11 @@
       <c r="N209" s="9"/>
       <c r="O209" s="9"/>
       <c r="P209" s="9"/>
-      <c r="Q209" s="9"/>
-      <c r="R209" s="9"/>
-      <c r="S209" s="9"/>
-      <c r="T209" s="9"/>
-      <c r="U209" s="9"/>
+      <c r="Q209" s="36"/>
+      <c r="R209" s="28"/>
+      <c r="S209" s="36"/>
+      <c r="T209" s="36"/>
+      <c r="U209" s="36"/>
       <c r="V209" s="9"/>
       <c r="W209" s="9"/>
       <c r="X209" s="9"/>
@@ -24590,11 +24652,11 @@
       <c r="N210" s="9"/>
       <c r="O210" s="9"/>
       <c r="P210" s="9"/>
-      <c r="Q210" s="9"/>
-      <c r="R210" s="9"/>
-      <c r="S210" s="9"/>
-      <c r="T210" s="9"/>
-      <c r="U210" s="9"/>
+      <c r="Q210" s="36"/>
+      <c r="R210" s="28"/>
+      <c r="S210" s="36"/>
+      <c r="T210" s="36"/>
+      <c r="U210" s="36"/>
       <c r="V210" s="9"/>
       <c r="W210" s="9"/>
       <c r="X210" s="9"/>
